--- a/docs/suivi-tests.xlsx
+++ b/docs/suivi-tests.xlsx
@@ -563,7 +563,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Dernier passage : 20/09/2026 15:22</t>
+          <t>Dernier passage : 20/09/2026 16:08</t>
         </is>
       </c>
     </row>
@@ -876,7 +876,7 @@
         </is>
       </c>
       <c r="G4" s="5" t="n">
-        <v>1.12</v>
+        <v>1.28</v>
       </c>
       <c r="H4" s="5" t="inlineStr"/>
       <c r="I4" s="5" t="inlineStr"/>
@@ -913,7 +913,7 @@
         </is>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="H5" s="5" t="inlineStr"/>
       <c r="I5" s="5" t="inlineStr"/>
@@ -950,7 +950,7 @@
         </is>
       </c>
       <c r="G6" s="5" t="n">
-        <v>1.99</v>
+        <v>2.62</v>
       </c>
       <c r="H6" s="5" t="inlineStr"/>
       <c r="I6" s="5" t="inlineStr"/>
@@ -987,7 +987,7 @@
         </is>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="H7" s="5" t="inlineStr"/>
       <c r="I7" s="5" t="inlineStr"/>
@@ -1024,7 +1024,7 @@
         </is>
       </c>
       <c r="G8" s="5" t="n">
-        <v>1.25</v>
+        <v>1.48</v>
       </c>
       <c r="H8" s="5" t="inlineStr"/>
       <c r="I8" s="5" t="inlineStr"/>
@@ -1061,7 +1061,7 @@
         </is>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.23</v>
       </c>
       <c r="H9" s="5" t="inlineStr"/>
       <c r="I9" s="5" t="inlineStr"/>
@@ -1098,7 +1098,7 @@
         </is>
       </c>
       <c r="G10" s="5" t="n">
-        <v>1.26</v>
+        <v>1.45</v>
       </c>
       <c r="H10" s="5" t="inlineStr"/>
       <c r="I10" s="5" t="inlineStr"/>
@@ -1135,7 +1135,7 @@
         </is>
       </c>
       <c r="G11" s="5" t="n">
-        <v>6.51</v>
+        <v>6.66</v>
       </c>
       <c r="H11" s="5" t="inlineStr"/>
       <c r="I11" s="5" t="inlineStr"/>
@@ -1172,7 +1172,7 @@
         </is>
       </c>
       <c r="G12" s="5" t="n">
-        <v>1.43</v>
+        <v>1.13</v>
       </c>
       <c r="H12" s="5" t="inlineStr"/>
       <c r="I12" s="5" t="inlineStr"/>
@@ -1209,7 +1209,7 @@
         </is>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.86</v>
+        <v>1.12</v>
       </c>
       <c r="H13" s="5" t="inlineStr"/>
       <c r="I13" s="5" t="inlineStr"/>
@@ -1246,7 +1246,7 @@
         </is>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.99</v>
+        <v>0.93</v>
       </c>
       <c r="H14" s="5" t="inlineStr"/>
       <c r="I14" s="5" t="inlineStr"/>
@@ -1283,7 +1283,7 @@
         </is>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.74</v>
+        <v>0.9</v>
       </c>
       <c r="H15" s="5" t="inlineStr"/>
       <c r="I15" s="5" t="inlineStr"/>

--- a/docs/suivi-tests.xlsx
+++ b/docs/suivi-tests.xlsx
@@ -642,7 +642,7 @@
       </c>
       <c r="H6" s="5" t="inlineStr">
         <is>
-          <t>16 / 57</t>
+          <t>16 / 58</t>
         </is>
       </c>
       <c r="I6" s="5" t="n">
@@ -669,12 +669,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>69 joués</t>
+          <t>71 joués</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>tous verts</t>
+          <t>1 en échec</t>
         </is>
       </c>
     </row>
@@ -1447,7 +1447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E60"/>
+  <dimension ref="A1:E61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2774,7 +2774,7 @@
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>C34</t>
+          <t>C33c</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
@@ -2799,7 +2799,7 @@
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>C35</t>
+          <t>C34</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
@@ -2824,20 +2824,20 @@
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>C36</t>
+          <t>C35</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>S02 Mot de passe erroné ; S06 Nom du club laissé vide</t>
+          <t>aucun parcours</t>
         </is>
       </c>
       <c r="D57" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E57" s="5" t="inlineStr">
         <is>
-          <t>Vert</t>
+          <t>Filet technique seul</t>
         </is>
       </c>
     </row>
@@ -2849,16 +2849,16 @@
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>C37</t>
+          <t>C36</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>S05 Le gérant modifie l'identité du club</t>
+          <t>S02 Mot de passe erroné ; S06 Nom du club laissé vide</t>
         </is>
       </c>
       <c r="D58" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E58" s="5" t="inlineStr">
         <is>
@@ -2874,20 +2874,20 @@
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>C38</t>
+          <t>C37</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>aucun parcours</t>
+          <t>S05 Le gérant modifie l'identité du club</t>
         </is>
       </c>
       <c r="D59" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E59" s="5" t="inlineStr">
         <is>
-          <t>Filet technique seul</t>
+          <t>Vert</t>
         </is>
       </c>
     </row>
@@ -2899,18 +2899,43 @@
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
+          <t>C38</t>
+        </is>
+      </c>
+      <c r="C60" s="5" t="inlineStr">
+        <is>
+          <t>aucun parcours</t>
+        </is>
+      </c>
+      <c r="D60" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E60" s="5" t="inlineStr">
+        <is>
+          <t>Filet technique seul</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="5" t="inlineStr">
+        <is>
+          <t>F01</t>
+        </is>
+      </c>
+      <c r="B61" s="5" t="inlineStr">
+        <is>
           <t>C39</t>
         </is>
       </c>
-      <c r="C60" s="5" t="inlineStr">
-        <is>
-          <t>aucun parcours</t>
-        </is>
-      </c>
-      <c r="D60" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E60" s="5" t="inlineStr">
+      <c r="C61" s="5" t="inlineStr">
+        <is>
+          <t>aucun parcours</t>
+        </is>
+      </c>
+      <c r="D61" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E61" s="5" t="inlineStr">
         <is>
           <t>Filet technique seul</t>
         </is>
@@ -2920,7 +2945,7 @@
   <mergeCells count="1">
     <mergeCell ref="A1:E1"/>
   </mergeCells>
-  <conditionalFormatting sqref="E4:E60">
+  <conditionalFormatting sqref="E4:E61">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"Vert"</formula>
     </cfRule>
@@ -2950,7 +2975,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3320,8 +3345,40 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>F01</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>L'accueil détenait `users.exporter` sans `users.consulter` : un droit inopérant, qui s'activait dès qu'on lui accordait la simple lecture</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>Question soulevée par la recette S08, démontrée par l'API</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>Le gérant accorde « consulter la liste » et ouvre sans le savoir l'export de la liste du personnel, contre le critère C33b</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>Tests techniques `ExportsApiTest.c33c` et `ArchitectureTest.exporterSupposeConsulter`</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>Close</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="F4:F13">
+  <conditionalFormatting sqref="F4:F14">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"Close"</formula>
     </cfRule>

--- a/docs/suivi-tests.xlsx
+++ b/docs/suivi-tests.xlsx
@@ -563,7 +563,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Dernier passage : 20/09/2026 16:08</t>
+          <t>Dernier passage : 20/09/2026 17:16</t>
         </is>
       </c>
     </row>
@@ -626,10 +626,10 @@
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E6" s="5" t="n">
         <v>0</v>
@@ -642,7 +642,7 @@
       </c>
       <c r="H6" s="5" t="inlineStr">
         <is>
-          <t>16 / 58</t>
+          <t>18 / 64</t>
         </is>
       </c>
       <c r="I6" s="5" t="n">
@@ -669,12 +669,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>71 joués</t>
+          <t>77 joués</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1 en échec</t>
+          <t>tous verts</t>
         </is>
       </c>
     </row>
@@ -776,7 +776,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I19"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -876,7 +876,7 @@
         </is>
       </c>
       <c r="G4" s="5" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="H4" s="5" t="inlineStr"/>
       <c r="I4" s="5" t="inlineStr"/>
@@ -913,7 +913,7 @@
         </is>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.71</v>
+        <v>0.89</v>
       </c>
       <c r="H5" s="5" t="inlineStr"/>
       <c r="I5" s="5" t="inlineStr"/>
@@ -950,7 +950,7 @@
         </is>
       </c>
       <c r="G6" s="5" t="n">
-        <v>2.62</v>
+        <v>2.92</v>
       </c>
       <c r="H6" s="5" t="inlineStr"/>
       <c r="I6" s="5" t="inlineStr"/>
@@ -987,7 +987,7 @@
         </is>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.8</v>
+        <v>1.22</v>
       </c>
       <c r="H7" s="5" t="inlineStr"/>
       <c r="I7" s="5" t="inlineStr"/>
@@ -1024,7 +1024,7 @@
         </is>
       </c>
       <c r="G8" s="5" t="n">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="H8" s="5" t="inlineStr"/>
       <c r="I8" s="5" t="inlineStr"/>
@@ -1061,7 +1061,7 @@
         </is>
       </c>
       <c r="G9" s="5" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="H9" s="5" t="inlineStr"/>
       <c r="I9" s="5" t="inlineStr"/>
@@ -1098,7 +1098,7 @@
         </is>
       </c>
       <c r="G10" s="5" t="n">
-        <v>1.45</v>
+        <v>1.55</v>
       </c>
       <c r="H10" s="5" t="inlineStr"/>
       <c r="I10" s="5" t="inlineStr"/>
@@ -1135,7 +1135,7 @@
         </is>
       </c>
       <c r="G11" s="5" t="n">
-        <v>6.66</v>
+        <v>1.71</v>
       </c>
       <c r="H11" s="5" t="inlineStr"/>
       <c r="I11" s="5" t="inlineStr"/>
@@ -1172,7 +1172,7 @@
         </is>
       </c>
       <c r="G12" s="5" t="n">
-        <v>1.13</v>
+        <v>1.42</v>
       </c>
       <c r="H12" s="5" t="inlineStr"/>
       <c r="I12" s="5" t="inlineStr"/>
@@ -1209,7 +1209,7 @@
         </is>
       </c>
       <c r="G13" s="5" t="n">
-        <v>1.12</v>
+        <v>1.25</v>
       </c>
       <c r="H13" s="5" t="inlineStr"/>
       <c r="I13" s="5" t="inlineStr"/>
@@ -1246,7 +1246,7 @@
         </is>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.93</v>
+        <v>1.21</v>
       </c>
       <c r="H14" s="5" t="inlineStr"/>
       <c r="I14" s="5" t="inlineStr"/>
@@ -1283,7 +1283,7 @@
         </is>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.9</v>
+        <v>1.23</v>
       </c>
       <c r="H15" s="5" t="inlineStr"/>
       <c r="I15" s="5" t="inlineStr"/>
@@ -1416,8 +1416,82 @@
       <c r="H19" s="5" t="inlineStr"/>
       <c r="I19" s="5" t="inlineStr"/>
     </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>S17</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>Le gérant entre sans second facteur et voit un rappel permanent</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>Rien ne bloque, le rappel est sur chaque écran et ne se ferme pas</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>C6g</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>Automatisé</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>Vert</t>
+        </is>
+      </c>
+      <c r="G20" s="5" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="H20" s="5" t="inlineStr"/>
+      <c r="I20" s="5" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>S18</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>L'accueil n'est jamais invitée à activer un second facteur</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>Le rappel ne s'adresse qu'aux rôles sensibles</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>C6k</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>Automatisé</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>Vert</t>
+        </is>
+      </c>
+      <c r="G21" s="5" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="H21" s="5" t="inlineStr"/>
+      <c r="I21" s="5" t="inlineStr"/>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="F4:F19">
+  <conditionalFormatting sqref="F4:F21">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"Vert"</formula>
     </cfRule>
@@ -1447,7 +1521,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E61"/>
+  <dimension ref="A1:E67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1774,7 +1848,7 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>C6f</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
@@ -1799,12 +1873,12 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>C8</t>
+          <t>C6g</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>S10 Se déconnecter</t>
+          <t>S17 Le gérant entre sans second facteur et voit un rappel permanent</t>
         </is>
       </c>
       <c r="D16" s="5" t="n">
@@ -1824,7 +1898,7 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>C8b</t>
+          <t>C6h</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
@@ -1849,20 +1923,20 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>C8c</t>
+          <t>C6i</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>S11 Recharger la page</t>
+          <t>aucun parcours</t>
         </is>
       </c>
       <c r="D18" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>Vert</t>
+          <t>Filet technique seul</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1948,7 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>C9</t>
+          <t>C6j</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
@@ -1899,20 +1973,20 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>C10</t>
+          <t>C6k</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>aucun parcours</t>
+          <t>S18 L'accueil n'est jamais invitée à activer un second facteur</t>
         </is>
       </c>
       <c r="D20" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>Filet technique seul</t>
+          <t>Vert</t>
         </is>
       </c>
     </row>
@@ -1924,20 +1998,20 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>C10b</t>
+          <t>C7</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>S03 Cinq échecs de suite verrouillent le compte</t>
+          <t>aucun parcours</t>
         </is>
       </c>
       <c r="D21" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>Vert</t>
+          <t>Filet technique seul</t>
         </is>
       </c>
     </row>
@@ -1949,12 +2023,12 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>C11</t>
+          <t>C8</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>S08 L'accueil consulte sans modifier, et n'atteint pas le journal</t>
+          <t>S10 Se déconnecter</t>
         </is>
       </c>
       <c r="D22" s="5" t="n">
@@ -1974,7 +2048,7 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>C11a</t>
+          <t>C8b</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
@@ -1999,20 +2073,20 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>C11b</t>
+          <t>C8c</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>aucun parcours</t>
+          <t>S11 Recharger la page</t>
         </is>
       </c>
       <c r="D24" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>Filet technique seul</t>
+          <t>Vert</t>
         </is>
       </c>
     </row>
@@ -2024,7 +2098,7 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>C11c</t>
+          <t>C9</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
@@ -2049,7 +2123,7 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>C12</t>
+          <t>C10</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
@@ -2074,20 +2148,20 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>C12a</t>
+          <t>C10b</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>aucun parcours</t>
+          <t>S03 Cinq échecs de suite verrouillent le compte</t>
         </is>
       </c>
       <c r="D27" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>Filet technique seul</t>
+          <t>Vert</t>
         </is>
       </c>
     </row>
@@ -2099,20 +2173,20 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>C12b</t>
+          <t>C11</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>aucun parcours</t>
+          <t>S08 L'accueil consulte sans modifier, et n'atteint pas le journal</t>
         </is>
       </c>
       <c r="D28" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>Filet technique seul</t>
+          <t>Vert</t>
         </is>
       </c>
     </row>
@@ -2124,7 +2198,7 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>C13</t>
+          <t>C11a</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
@@ -2149,7 +2223,7 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>C14</t>
+          <t>C11b</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
@@ -2174,7 +2248,7 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>C15</t>
+          <t>C11c</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
@@ -2199,20 +2273,20 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>C16</t>
+          <t>C12</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>S05 Le gérant modifie l'identité du club</t>
+          <t>aucun parcours</t>
         </is>
       </c>
       <c r="D32" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t>Vert</t>
+          <t>Filet technique seul</t>
         </is>
       </c>
     </row>
@@ -2224,7 +2298,7 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>C16b</t>
+          <t>C12a</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
@@ -2249,7 +2323,7 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>C16c</t>
+          <t>C12b</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
@@ -2274,7 +2348,7 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>C17</t>
+          <t>C13</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
@@ -2299,7 +2373,7 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>C18</t>
+          <t>C14</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
@@ -2324,20 +2398,20 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>C19</t>
+          <t>C15</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>S08 L'accueil consulte sans modifier, et n'atteint pas le journal</t>
+          <t>aucun parcours</t>
         </is>
       </c>
       <c r="D37" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t>Vert</t>
+          <t>Filet technique seul</t>
         </is>
       </c>
     </row>
@@ -2349,12 +2423,12 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>C19b</t>
+          <t>C16</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>S09 Filtrer le journal d'audit</t>
+          <t>S05 Le gérant modifie l'identité du club</t>
         </is>
       </c>
       <c r="D38" s="5" t="n">
@@ -2374,7 +2448,7 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>C20</t>
+          <t>C16b</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
@@ -2399,7 +2473,7 @@
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>C21</t>
+          <t>C16c</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
@@ -2424,7 +2498,7 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>C22</t>
+          <t>C17</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
@@ -2449,7 +2523,7 @@
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>C22b</t>
+          <t>C18</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
@@ -2474,20 +2548,20 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>C23</t>
+          <t>C19</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>aucun parcours</t>
+          <t>S08 L'accueil consulte sans modifier, et n'atteint pas le journal</t>
         </is>
       </c>
       <c r="D43" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
-          <t>Filet technique seul</t>
+          <t>Vert</t>
         </is>
       </c>
     </row>
@@ -2499,20 +2573,20 @@
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>C24</t>
+          <t>C19b</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>aucun parcours</t>
+          <t>S09 Filtrer le journal d'audit</t>
         </is>
       </c>
       <c r="D44" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E44" s="5" t="inlineStr">
         <is>
-          <t>Filet technique seul</t>
+          <t>Vert</t>
         </is>
       </c>
     </row>
@@ -2524,7 +2598,7 @@
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>C25</t>
+          <t>C20</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
@@ -2549,7 +2623,7 @@
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>C26</t>
+          <t>C21</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
@@ -2574,7 +2648,7 @@
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>C27</t>
+          <t>C22</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
@@ -2599,20 +2673,20 @@
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>C28</t>
+          <t>C22b</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>S05 Le gérant modifie l'identité du club</t>
+          <t>aucun parcours</t>
         </is>
       </c>
       <c r="D48" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E48" s="5" t="inlineStr">
         <is>
-          <t>Vert</t>
+          <t>Filet technique seul</t>
         </is>
       </c>
     </row>
@@ -2624,20 +2698,20 @@
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>C29</t>
+          <t>C23</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>S07 Consulter la liste des utilisateurs</t>
+          <t>aucun parcours</t>
         </is>
       </c>
       <c r="D49" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E49" s="5" t="inlineStr">
         <is>
-          <t>Vert</t>
+          <t>Filet technique seul</t>
         </is>
       </c>
     </row>
@@ -2649,7 +2723,7 @@
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>C30</t>
+          <t>C24</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
@@ -2674,20 +2748,20 @@
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>C31</t>
+          <t>C25</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>S12 Lire les règles configurables du club</t>
+          <t>aucun parcours</t>
         </is>
       </c>
       <c r="D51" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E51" s="5" t="inlineStr">
         <is>
-          <t>Vert</t>
+          <t>Filet technique seul</t>
         </is>
       </c>
     </row>
@@ -2699,20 +2773,20 @@
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>C32</t>
+          <t>C26</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>S08 L'accueil consulte sans modifier, et n'atteint pas le journal</t>
+          <t>aucun parcours</t>
         </is>
       </c>
       <c r="D52" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E52" s="5" t="inlineStr">
         <is>
-          <t>Vert</t>
+          <t>Filet technique seul</t>
         </is>
       </c>
     </row>
@@ -2724,7 +2798,7 @@
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>C33</t>
+          <t>C27</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
@@ -2749,20 +2823,20 @@
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>C33b</t>
+          <t>C28</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>aucun parcours</t>
+          <t>S05 Le gérant modifie l'identité du club</t>
         </is>
       </c>
       <c r="D54" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E54" s="5" t="inlineStr">
         <is>
-          <t>Filet technique seul</t>
+          <t>Vert</t>
         </is>
       </c>
     </row>
@@ -2774,20 +2848,20 @@
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>C33c</t>
+          <t>C29</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>aucun parcours</t>
+          <t>S07 Consulter la liste des utilisateurs</t>
         </is>
       </c>
       <c r="D55" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E55" s="5" t="inlineStr">
         <is>
-          <t>Filet technique seul</t>
+          <t>Vert</t>
         </is>
       </c>
     </row>
@@ -2799,7 +2873,7 @@
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>C34</t>
+          <t>C30</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
@@ -2824,20 +2898,20 @@
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>C35</t>
+          <t>C31</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>aucun parcours</t>
+          <t>S12 Lire les règles configurables du club</t>
         </is>
       </c>
       <c r="D57" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E57" s="5" t="inlineStr">
         <is>
-          <t>Filet technique seul</t>
+          <t>Vert</t>
         </is>
       </c>
     </row>
@@ -2849,16 +2923,16 @@
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>C36</t>
+          <t>C32</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>S02 Mot de passe erroné ; S06 Nom du club laissé vide</t>
+          <t>S08 L'accueil consulte sans modifier, et n'atteint pas le journal</t>
         </is>
       </c>
       <c r="D58" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E58" s="5" t="inlineStr">
         <is>
@@ -2874,20 +2948,20 @@
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>C37</t>
+          <t>C33</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>S05 Le gérant modifie l'identité du club</t>
+          <t>aucun parcours</t>
         </is>
       </c>
       <c r="D59" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E59" s="5" t="inlineStr">
         <is>
-          <t>Vert</t>
+          <t>Filet technique seul</t>
         </is>
       </c>
     </row>
@@ -2899,7 +2973,7 @@
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>C38</t>
+          <t>C33b</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
@@ -2924,18 +2998,168 @@
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
+          <t>C33c</t>
+        </is>
+      </c>
+      <c r="C61" s="5" t="inlineStr">
+        <is>
+          <t>aucun parcours</t>
+        </is>
+      </c>
+      <c r="D61" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E61" s="5" t="inlineStr">
+        <is>
+          <t>Filet technique seul</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="5" t="inlineStr">
+        <is>
+          <t>F01</t>
+        </is>
+      </c>
+      <c r="B62" s="5" t="inlineStr">
+        <is>
+          <t>C34</t>
+        </is>
+      </c>
+      <c r="C62" s="5" t="inlineStr">
+        <is>
+          <t>aucun parcours</t>
+        </is>
+      </c>
+      <c r="D62" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E62" s="5" t="inlineStr">
+        <is>
+          <t>Filet technique seul</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="5" t="inlineStr">
+        <is>
+          <t>F01</t>
+        </is>
+      </c>
+      <c r="B63" s="5" t="inlineStr">
+        <is>
+          <t>C35</t>
+        </is>
+      </c>
+      <c r="C63" s="5" t="inlineStr">
+        <is>
+          <t>aucun parcours</t>
+        </is>
+      </c>
+      <c r="D63" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E63" s="5" t="inlineStr">
+        <is>
+          <t>Filet technique seul</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="5" t="inlineStr">
+        <is>
+          <t>F01</t>
+        </is>
+      </c>
+      <c r="B64" s="5" t="inlineStr">
+        <is>
+          <t>C36</t>
+        </is>
+      </c>
+      <c r="C64" s="5" t="inlineStr">
+        <is>
+          <t>S02 Mot de passe erroné ; S06 Nom du club laissé vide</t>
+        </is>
+      </c>
+      <c r="D64" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E64" s="5" t="inlineStr">
+        <is>
+          <t>Vert</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="5" t="inlineStr">
+        <is>
+          <t>F01</t>
+        </is>
+      </c>
+      <c r="B65" s="5" t="inlineStr">
+        <is>
+          <t>C37</t>
+        </is>
+      </c>
+      <c r="C65" s="5" t="inlineStr">
+        <is>
+          <t>S05 Le gérant modifie l'identité du club</t>
+        </is>
+      </c>
+      <c r="D65" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E65" s="5" t="inlineStr">
+        <is>
+          <t>Vert</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="5" t="inlineStr">
+        <is>
+          <t>F01</t>
+        </is>
+      </c>
+      <c r="B66" s="5" t="inlineStr">
+        <is>
+          <t>C38</t>
+        </is>
+      </c>
+      <c r="C66" s="5" t="inlineStr">
+        <is>
+          <t>aucun parcours</t>
+        </is>
+      </c>
+      <c r="D66" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E66" s="5" t="inlineStr">
+        <is>
+          <t>Filet technique seul</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="5" t="inlineStr">
+        <is>
+          <t>F01</t>
+        </is>
+      </c>
+      <c r="B67" s="5" t="inlineStr">
+        <is>
           <t>C39</t>
         </is>
       </c>
-      <c r="C61" s="5" t="inlineStr">
-        <is>
-          <t>aucun parcours</t>
-        </is>
-      </c>
-      <c r="D61" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E61" s="5" t="inlineStr">
+      <c r="C67" s="5" t="inlineStr">
+        <is>
+          <t>aucun parcours</t>
+        </is>
+      </c>
+      <c r="D67" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E67" s="5" t="inlineStr">
         <is>
           <t>Filet technique seul</t>
         </is>
@@ -2945,7 +3169,7 @@
   <mergeCells count="1">
     <mergeCell ref="A1:E1"/>
   </mergeCells>
-  <conditionalFormatting sqref="E4:E61">
+  <conditionalFormatting sqref="E4:E67">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"Vert"</formula>
     </cfRule>

--- a/docs/suivi-tests.xlsx
+++ b/docs/suivi-tests.xlsx
@@ -563,7 +563,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Dernier passage : 20/09/2026 17:16</t>
+          <t>Dernier passage : 20/09/2026 17:31</t>
         </is>
       </c>
     </row>
@@ -626,10 +626,10 @@
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E6" s="5" t="n">
         <v>0</v>
@@ -642,7 +642,7 @@
       </c>
       <c r="H6" s="5" t="inlineStr">
         <is>
-          <t>18 / 64</t>
+          <t>19 / 65</t>
         </is>
       </c>
       <c r="I6" s="5" t="n">
@@ -776,7 +776,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -876,7 +876,7 @@
         </is>
       </c>
       <c r="G4" s="5" t="n">
-        <v>1.32</v>
+        <v>0.97</v>
       </c>
       <c r="H4" s="5" t="inlineStr"/>
       <c r="I4" s="5" t="inlineStr"/>
@@ -913,7 +913,7 @@
         </is>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.89</v>
+        <v>0.51</v>
       </c>
       <c r="H5" s="5" t="inlineStr"/>
       <c r="I5" s="5" t="inlineStr"/>
@@ -950,7 +950,7 @@
         </is>
       </c>
       <c r="G6" s="5" t="n">
-        <v>2.92</v>
+        <v>1.82</v>
       </c>
       <c r="H6" s="5" t="inlineStr"/>
       <c r="I6" s="5" t="inlineStr"/>
@@ -987,7 +987,7 @@
         </is>
       </c>
       <c r="G7" s="5" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="H7" s="5" t="inlineStr"/>
       <c r="I7" s="5" t="inlineStr"/>
@@ -1024,7 +1024,7 @@
         </is>
       </c>
       <c r="G8" s="5" t="n">
-        <v>1.51</v>
+        <v>1.07</v>
       </c>
       <c r="H8" s="5" t="inlineStr"/>
       <c r="I8" s="5" t="inlineStr"/>
@@ -1061,7 +1061,7 @@
         </is>
       </c>
       <c r="G9" s="5" t="n">
-        <v>1.25</v>
+        <v>0.89</v>
       </c>
       <c r="H9" s="5" t="inlineStr"/>
       <c r="I9" s="5" t="inlineStr"/>
@@ -1098,7 +1098,7 @@
         </is>
       </c>
       <c r="G10" s="5" t="n">
-        <v>1.55</v>
+        <v>1.11</v>
       </c>
       <c r="H10" s="5" t="inlineStr"/>
       <c r="I10" s="5" t="inlineStr"/>
@@ -1135,7 +1135,7 @@
         </is>
       </c>
       <c r="G11" s="5" t="n">
-        <v>1.71</v>
+        <v>6.38</v>
       </c>
       <c r="H11" s="5" t="inlineStr"/>
       <c r="I11" s="5" t="inlineStr"/>
@@ -1172,7 +1172,7 @@
         </is>
       </c>
       <c r="G12" s="5" t="n">
-        <v>1.42</v>
+        <v>0.97</v>
       </c>
       <c r="H12" s="5" t="inlineStr"/>
       <c r="I12" s="5" t="inlineStr"/>
@@ -1209,7 +1209,7 @@
         </is>
       </c>
       <c r="G13" s="5" t="n">
-        <v>1.25</v>
+        <v>0.85</v>
       </c>
       <c r="H13" s="5" t="inlineStr"/>
       <c r="I13" s="5" t="inlineStr"/>
@@ -1246,7 +1246,7 @@
         </is>
       </c>
       <c r="G14" s="5" t="n">
-        <v>1.21</v>
+        <v>0.75</v>
       </c>
       <c r="H14" s="5" t="inlineStr"/>
       <c r="I14" s="5" t="inlineStr"/>
@@ -1283,7 +1283,7 @@
         </is>
       </c>
       <c r="G15" s="5" t="n">
-        <v>1.23</v>
+        <v>0.61</v>
       </c>
       <c r="H15" s="5" t="inlineStr"/>
       <c r="I15" s="5" t="inlineStr"/>
@@ -1448,7 +1448,7 @@
         </is>
       </c>
       <c r="G20" s="5" t="n">
-        <v>1.14</v>
+        <v>0.83</v>
       </c>
       <c r="H20" s="5" t="inlineStr"/>
       <c r="I20" s="5" t="inlineStr"/>
@@ -1485,13 +1485,50 @@
         </is>
       </c>
       <c r="G21" s="5" t="n">
-        <v>1.21</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H21" s="5" t="inlineStr"/>
       <c r="I21" s="5" t="inlineStr"/>
     </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>S19</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>Le gérant change la couleur du club</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>La couleur s'applique à l'écran dès l'enregistrement et survit au rechargement</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>C28b</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>Automatisé</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t>Vert</t>
+        </is>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="H22" s="5" t="inlineStr"/>
+      <c r="I22" s="5" t="inlineStr"/>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="F4:F21">
+  <conditionalFormatting sqref="F4:F22">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"Vert"</formula>
     </cfRule>
@@ -1521,7 +1558,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E67"/>
+  <dimension ref="A1:E68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2848,12 +2885,12 @@
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>C29</t>
+          <t>C28b</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>S07 Consulter la liste des utilisateurs</t>
+          <t>S19 Le gérant change la couleur du club</t>
         </is>
       </c>
       <c r="D55" s="5" t="n">
@@ -2873,20 +2910,20 @@
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>C30</t>
+          <t>C29</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>aucun parcours</t>
+          <t>S07 Consulter la liste des utilisateurs</t>
         </is>
       </c>
       <c r="D56" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E56" s="5" t="inlineStr">
         <is>
-          <t>Filet technique seul</t>
+          <t>Vert</t>
         </is>
       </c>
     </row>
@@ -2898,20 +2935,20 @@
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>C31</t>
+          <t>C30</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>S12 Lire les règles configurables du club</t>
+          <t>aucun parcours</t>
         </is>
       </c>
       <c r="D57" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E57" s="5" t="inlineStr">
         <is>
-          <t>Vert</t>
+          <t>Filet technique seul</t>
         </is>
       </c>
     </row>
@@ -2923,12 +2960,12 @@
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>C32</t>
+          <t>C31</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>S08 L'accueil consulte sans modifier, et n'atteint pas le journal</t>
+          <t>S12 Lire les règles configurables du club</t>
         </is>
       </c>
       <c r="D58" s="5" t="n">
@@ -2948,20 +2985,20 @@
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>C33</t>
+          <t>C32</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>aucun parcours</t>
+          <t>S08 L'accueil consulte sans modifier, et n'atteint pas le journal</t>
         </is>
       </c>
       <c r="D59" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E59" s="5" t="inlineStr">
         <is>
-          <t>Filet technique seul</t>
+          <t>Vert</t>
         </is>
       </c>
     </row>
@@ -2973,7 +3010,7 @@
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>C33b</t>
+          <t>C33</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
@@ -2998,7 +3035,7 @@
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>C33c</t>
+          <t>C33b</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
@@ -3023,7 +3060,7 @@
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>C34</t>
+          <t>C33c</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
@@ -3048,7 +3085,7 @@
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>C35</t>
+          <t>C34</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
@@ -3073,20 +3110,20 @@
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>C36</t>
+          <t>C35</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>S02 Mot de passe erroné ; S06 Nom du club laissé vide</t>
+          <t>aucun parcours</t>
         </is>
       </c>
       <c r="D64" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E64" s="5" t="inlineStr">
         <is>
-          <t>Vert</t>
+          <t>Filet technique seul</t>
         </is>
       </c>
     </row>
@@ -3098,16 +3135,16 @@
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>C37</t>
+          <t>C36</t>
         </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>S05 Le gérant modifie l'identité du club</t>
+          <t>S02 Mot de passe erroné ; S06 Nom du club laissé vide</t>
         </is>
       </c>
       <c r="D65" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E65" s="5" t="inlineStr">
         <is>
@@ -3123,20 +3160,20 @@
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>C38</t>
+          <t>C37</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>aucun parcours</t>
+          <t>S05 Le gérant modifie l'identité du club</t>
         </is>
       </c>
       <c r="D66" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E66" s="5" t="inlineStr">
         <is>
-          <t>Filet technique seul</t>
+          <t>Vert</t>
         </is>
       </c>
     </row>
@@ -3148,18 +3185,43 @@
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
+          <t>C38</t>
+        </is>
+      </c>
+      <c r="C67" s="5" t="inlineStr">
+        <is>
+          <t>aucun parcours</t>
+        </is>
+      </c>
+      <c r="D67" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E67" s="5" t="inlineStr">
+        <is>
+          <t>Filet technique seul</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="5" t="inlineStr">
+        <is>
+          <t>F01</t>
+        </is>
+      </c>
+      <c r="B68" s="5" t="inlineStr">
+        <is>
           <t>C39</t>
         </is>
       </c>
-      <c r="C67" s="5" t="inlineStr">
-        <is>
-          <t>aucun parcours</t>
-        </is>
-      </c>
-      <c r="D67" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E67" s="5" t="inlineStr">
+      <c r="C68" s="5" t="inlineStr">
+        <is>
+          <t>aucun parcours</t>
+        </is>
+      </c>
+      <c r="D68" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E68" s="5" t="inlineStr">
         <is>
           <t>Filet technique seul</t>
         </is>
@@ -3169,7 +3231,7 @@
   <mergeCells count="1">
     <mergeCell ref="A1:E1"/>
   </mergeCells>
-  <conditionalFormatting sqref="E4:E67">
+  <conditionalFormatting sqref="E4:E68">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"Vert"</formula>
     </cfRule>

--- a/docs/suivi-tests.xlsx
+++ b/docs/suivi-tests.xlsx
@@ -563,7 +563,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Dernier passage : 20/09/2026 17:31</t>
+          <t>Dernier passage : 20/09/2026 17:43</t>
         </is>
       </c>
     </row>
@@ -626,10 +626,10 @@
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E6" s="5" t="n">
         <v>0</v>
@@ -642,7 +642,7 @@
       </c>
       <c r="H6" s="5" t="inlineStr">
         <is>
-          <t>19 / 65</t>
+          <t>20 / 66</t>
         </is>
       </c>
       <c r="I6" s="5" t="n">
@@ -669,7 +669,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>77 joués</t>
+          <t>78 joués</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -776,7 +776,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I22"/>
+  <dimension ref="A1:I23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -876,7 +876,7 @@
         </is>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.97</v>
+        <v>0.95</v>
       </c>
       <c r="H4" s="5" t="inlineStr"/>
       <c r="I4" s="5" t="inlineStr"/>
@@ -913,7 +913,7 @@
         </is>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.51</v>
+        <v>0.5</v>
       </c>
       <c r="H5" s="5" t="inlineStr"/>
       <c r="I5" s="5" t="inlineStr"/>
@@ -950,7 +950,7 @@
         </is>
       </c>
       <c r="G6" s="5" t="n">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="H6" s="5" t="inlineStr"/>
       <c r="I6" s="5" t="inlineStr"/>
@@ -987,7 +987,7 @@
         </is>
       </c>
       <c r="G7" s="5" t="n">
-        <v>1.3</v>
+        <v>4.85</v>
       </c>
       <c r="H7" s="5" t="inlineStr"/>
       <c r="I7" s="5" t="inlineStr"/>
@@ -1024,7 +1024,7 @@
         </is>
       </c>
       <c r="G8" s="5" t="n">
-        <v>1.07</v>
+        <v>1.2</v>
       </c>
       <c r="H8" s="5" t="inlineStr"/>
       <c r="I8" s="5" t="inlineStr"/>
@@ -1061,7 +1061,7 @@
         </is>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.89</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H9" s="5" t="inlineStr"/>
       <c r="I9" s="5" t="inlineStr"/>
@@ -1098,7 +1098,7 @@
         </is>
       </c>
       <c r="G10" s="5" t="n">
-        <v>1.11</v>
+        <v>1.19</v>
       </c>
       <c r="H10" s="5" t="inlineStr"/>
       <c r="I10" s="5" t="inlineStr"/>
@@ -1135,7 +1135,7 @@
         </is>
       </c>
       <c r="G11" s="5" t="n">
-        <v>6.38</v>
+        <v>6.37</v>
       </c>
       <c r="H11" s="5" t="inlineStr"/>
       <c r="I11" s="5" t="inlineStr"/>
@@ -1172,7 +1172,7 @@
         </is>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.97</v>
+        <v>1.04</v>
       </c>
       <c r="H12" s="5" t="inlineStr"/>
       <c r="I12" s="5" t="inlineStr"/>
@@ -1209,7 +1209,7 @@
         </is>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.85</v>
+        <v>0.67</v>
       </c>
       <c r="H13" s="5" t="inlineStr"/>
       <c r="I13" s="5" t="inlineStr"/>
@@ -1246,7 +1246,7 @@
         </is>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.75</v>
+        <v>0.83</v>
       </c>
       <c r="H14" s="5" t="inlineStr"/>
       <c r="I14" s="5" t="inlineStr"/>
@@ -1283,7 +1283,7 @@
         </is>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.61</v>
+        <v>0.59</v>
       </c>
       <c r="H15" s="5" t="inlineStr"/>
       <c r="I15" s="5" t="inlineStr"/>
@@ -1448,7 +1448,7 @@
         </is>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.83</v>
+        <v>0.89</v>
       </c>
       <c r="H20" s="5" t="inlineStr"/>
       <c r="I20" s="5" t="inlineStr"/>
@@ -1485,7 +1485,7 @@
         </is>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.77</v>
       </c>
       <c r="H21" s="5" t="inlineStr"/>
       <c r="I21" s="5" t="inlineStr"/>
@@ -1522,13 +1522,50 @@
         </is>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.95</v>
+        <v>0.99</v>
       </c>
       <c r="H22" s="5" t="inlineStr"/>
       <c r="I22" s="5" t="inlineStr"/>
     </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>S20</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>Le gérant modifie une règle configurable</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>La valeur saisie est retenue, survit au rechargement, et l'origine passe à « choix du club »</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>C31b</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>Automatisé</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>Vert</t>
+        </is>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="H23" s="5" t="inlineStr"/>
+      <c r="I23" s="5" t="inlineStr"/>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="F4:F22">
+  <conditionalFormatting sqref="F4:F23">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"Vert"</formula>
     </cfRule>
@@ -1558,7 +1595,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E68"/>
+  <dimension ref="A1:E69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2985,12 +3022,12 @@
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>C32</t>
+          <t>C31b</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>S08 L'accueil consulte sans modifier, et n'atteint pas le journal</t>
+          <t>S20 Le gérant modifie une règle configurable</t>
         </is>
       </c>
       <c r="D59" s="5" t="n">
@@ -3010,20 +3047,20 @@
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>C33</t>
+          <t>C32</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>aucun parcours</t>
+          <t>S08 L'accueil consulte sans modifier, et n'atteint pas le journal</t>
         </is>
       </c>
       <c r="D60" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E60" s="5" t="inlineStr">
         <is>
-          <t>Filet technique seul</t>
+          <t>Vert</t>
         </is>
       </c>
     </row>
@@ -3035,7 +3072,7 @@
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>C33b</t>
+          <t>C33</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
@@ -3060,7 +3097,7 @@
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>C33c</t>
+          <t>C33b</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
@@ -3085,7 +3122,7 @@
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>C34</t>
+          <t>C33c</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
@@ -3110,7 +3147,7 @@
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>C35</t>
+          <t>C34</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
@@ -3135,20 +3172,20 @@
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>C36</t>
+          <t>C35</t>
         </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>S02 Mot de passe erroné ; S06 Nom du club laissé vide</t>
+          <t>aucun parcours</t>
         </is>
       </c>
       <c r="D65" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E65" s="5" t="inlineStr">
         <is>
-          <t>Vert</t>
+          <t>Filet technique seul</t>
         </is>
       </c>
     </row>
@@ -3160,16 +3197,16 @@
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>C37</t>
+          <t>C36</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>S05 Le gérant modifie l'identité du club</t>
+          <t>S02 Mot de passe erroné ; S06 Nom du club laissé vide</t>
         </is>
       </c>
       <c r="D66" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E66" s="5" t="inlineStr">
         <is>
@@ -3185,20 +3222,20 @@
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>C38</t>
+          <t>C37</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>aucun parcours</t>
+          <t>S05 Le gérant modifie l'identité du club</t>
         </is>
       </c>
       <c r="D67" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E67" s="5" t="inlineStr">
         <is>
-          <t>Filet technique seul</t>
+          <t>Vert</t>
         </is>
       </c>
     </row>
@@ -3210,18 +3247,43 @@
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
+          <t>C38</t>
+        </is>
+      </c>
+      <c r="C68" s="5" t="inlineStr">
+        <is>
+          <t>aucun parcours</t>
+        </is>
+      </c>
+      <c r="D68" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E68" s="5" t="inlineStr">
+        <is>
+          <t>Filet technique seul</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="5" t="inlineStr">
+        <is>
+          <t>F01</t>
+        </is>
+      </c>
+      <c r="B69" s="5" t="inlineStr">
+        <is>
           <t>C39</t>
         </is>
       </c>
-      <c r="C68" s="5" t="inlineStr">
-        <is>
-          <t>aucun parcours</t>
-        </is>
-      </c>
-      <c r="D68" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E68" s="5" t="inlineStr">
+      <c r="C69" s="5" t="inlineStr">
+        <is>
+          <t>aucun parcours</t>
+        </is>
+      </c>
+      <c r="D69" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E69" s="5" t="inlineStr">
         <is>
           <t>Filet technique seul</t>
         </is>
@@ -3231,7 +3293,7 @@
   <mergeCells count="1">
     <mergeCell ref="A1:E1"/>
   </mergeCells>
-  <conditionalFormatting sqref="E4:E68">
+  <conditionalFormatting sqref="E4:E69">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"Vert"</formula>
     </cfRule>

--- a/docs/suivi-tests.xlsx
+++ b/docs/suivi-tests.xlsx
@@ -563,7 +563,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Dernier passage : 20/09/2026 17:43</t>
+          <t>Dernier passage : 20/09/2026 17:53</t>
         </is>
       </c>
     </row>
@@ -626,10 +626,10 @@
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E6" s="5" t="n">
         <v>0</v>
@@ -642,7 +642,7 @@
       </c>
       <c r="H6" s="5" t="inlineStr">
         <is>
-          <t>20 / 66</t>
+          <t>22 / 70</t>
         </is>
       </c>
       <c r="I6" s="5" t="n">
@@ -669,7 +669,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>78 joués</t>
+          <t>82 joués</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -776,7 +776,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I23"/>
+  <dimension ref="A1:I24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -876,7 +876,7 @@
         </is>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.95</v>
+        <v>0.93</v>
       </c>
       <c r="H4" s="5" t="inlineStr"/>
       <c r="I4" s="5" t="inlineStr"/>
@@ -913,7 +913,7 @@
         </is>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="H5" s="5" t="inlineStr"/>
       <c r="I5" s="5" t="inlineStr"/>
@@ -950,7 +950,7 @@
         </is>
       </c>
       <c r="G6" s="5" t="n">
-        <v>1.85</v>
+        <v>1.94</v>
       </c>
       <c r="H6" s="5" t="inlineStr"/>
       <c r="I6" s="5" t="inlineStr"/>
@@ -987,7 +987,7 @@
         </is>
       </c>
       <c r="G7" s="5" t="n">
-        <v>4.85</v>
+        <v>1.32</v>
       </c>
       <c r="H7" s="5" t="inlineStr"/>
       <c r="I7" s="5" t="inlineStr"/>
@@ -1024,7 +1024,7 @@
         </is>
       </c>
       <c r="G8" s="5" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="H8" s="5" t="inlineStr"/>
       <c r="I8" s="5" t="inlineStr"/>
@@ -1061,7 +1061,7 @@
         </is>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.85</v>
       </c>
       <c r="H9" s="5" t="inlineStr"/>
       <c r="I9" s="5" t="inlineStr"/>
@@ -1098,7 +1098,7 @@
         </is>
       </c>
       <c r="G10" s="5" t="n">
-        <v>1.19</v>
+        <v>1.12</v>
       </c>
       <c r="H10" s="5" t="inlineStr"/>
       <c r="I10" s="5" t="inlineStr"/>
@@ -1135,7 +1135,7 @@
         </is>
       </c>
       <c r="G11" s="5" t="n">
-        <v>6.37</v>
+        <v>6.3</v>
       </c>
       <c r="H11" s="5" t="inlineStr"/>
       <c r="I11" s="5" t="inlineStr"/>
@@ -1172,7 +1172,7 @@
         </is>
       </c>
       <c r="G12" s="5" t="n">
-        <v>1.04</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H12" s="5" t="inlineStr"/>
       <c r="I12" s="5" t="inlineStr"/>
@@ -1209,7 +1209,7 @@
         </is>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.67</v>
+        <v>0.72</v>
       </c>
       <c r="H13" s="5" t="inlineStr"/>
       <c r="I13" s="5" t="inlineStr"/>
@@ -1246,7 +1246,7 @@
         </is>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.83</v>
+        <v>1.04</v>
       </c>
       <c r="H14" s="5" t="inlineStr"/>
       <c r="I14" s="5" t="inlineStr"/>
@@ -1448,7 +1448,7 @@
         </is>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.89</v>
+        <v>0.84</v>
       </c>
       <c r="H20" s="5" t="inlineStr"/>
       <c r="I20" s="5" t="inlineStr"/>
@@ -1485,7 +1485,7 @@
         </is>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="H21" s="5" t="inlineStr"/>
       <c r="I21" s="5" t="inlineStr"/>
@@ -1522,7 +1522,7 @@
         </is>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.99</v>
+        <v>0.96</v>
       </c>
       <c r="H22" s="5" t="inlineStr"/>
       <c r="I22" s="5" t="inlineStr"/>
@@ -1559,13 +1559,50 @@
         </is>
       </c>
       <c r="G23" s="5" t="n">
-        <v>1.02</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H23" s="5" t="inlineStr"/>
       <c r="I23" s="5" t="inlineStr"/>
     </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>S21</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>La liste des utilisateurs se parcourt page par page</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>La page s'ouvre à la taille retenue par le club, la plage affichée est juste, et changer la taille ramène au début</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>C40, C40c</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>Automatisé</t>
+        </is>
+      </c>
+      <c r="F24" s="5" t="inlineStr">
+        <is>
+          <t>Vert</t>
+        </is>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="H24" s="5" t="inlineStr"/>
+      <c r="I24" s="5" t="inlineStr"/>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="F4:F23">
+  <conditionalFormatting sqref="F4:F24">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"Vert"</formula>
     </cfRule>
@@ -1595,7 +1632,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E69"/>
+  <dimension ref="A1:E73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3289,11 +3326,111 @@
         </is>
       </c>
     </row>
+    <row r="70">
+      <c r="A70" s="5" t="inlineStr">
+        <is>
+          <t>F01</t>
+        </is>
+      </c>
+      <c r="B70" s="5" t="inlineStr">
+        <is>
+          <t>C40</t>
+        </is>
+      </c>
+      <c r="C70" s="5" t="inlineStr">
+        <is>
+          <t>S21 La liste des utilisateurs se parcourt page par page</t>
+        </is>
+      </c>
+      <c r="D70" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E70" s="5" t="inlineStr">
+        <is>
+          <t>Vert</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="5" t="inlineStr">
+        <is>
+          <t>F01</t>
+        </is>
+      </c>
+      <c r="B71" s="5" t="inlineStr">
+        <is>
+          <t>C40b</t>
+        </is>
+      </c>
+      <c r="C71" s="5" t="inlineStr">
+        <is>
+          <t>aucun parcours</t>
+        </is>
+      </c>
+      <c r="D71" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E71" s="5" t="inlineStr">
+        <is>
+          <t>Filet technique seul</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="5" t="inlineStr">
+        <is>
+          <t>F01</t>
+        </is>
+      </c>
+      <c r="B72" s="5" t="inlineStr">
+        <is>
+          <t>C40c</t>
+        </is>
+      </c>
+      <c r="C72" s="5" t="inlineStr">
+        <is>
+          <t>S21 La liste des utilisateurs se parcourt page par page</t>
+        </is>
+      </c>
+      <c r="D72" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E72" s="5" t="inlineStr">
+        <is>
+          <t>Vert</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="5" t="inlineStr">
+        <is>
+          <t>F01</t>
+        </is>
+      </c>
+      <c r="B73" s="5" t="inlineStr">
+        <is>
+          <t>C40d</t>
+        </is>
+      </c>
+      <c r="C73" s="5" t="inlineStr">
+        <is>
+          <t>aucun parcours</t>
+        </is>
+      </c>
+      <c r="D73" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E73" s="5" t="inlineStr">
+        <is>
+          <t>Filet technique seul</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:E1"/>
   </mergeCells>
-  <conditionalFormatting sqref="E4:E69">
+  <conditionalFormatting sqref="E4:E73">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"Vert"</formula>
     </cfRule>

--- a/docs/suivi-tests.xlsx
+++ b/docs/suivi-tests.xlsx
@@ -563,7 +563,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Dernier passage : 20/09/2026 17:53</t>
+          <t>Dernier passage : 20/09/2026 18:01</t>
         </is>
       </c>
     </row>
@@ -876,7 +876,7 @@
         </is>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.93</v>
+        <v>1.16</v>
       </c>
       <c r="H4" s="5" t="inlineStr"/>
       <c r="I4" s="5" t="inlineStr"/>
@@ -913,7 +913,7 @@
         </is>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.51</v>
+        <v>0.64</v>
       </c>
       <c r="H5" s="5" t="inlineStr"/>
       <c r="I5" s="5" t="inlineStr"/>
@@ -950,7 +950,7 @@
         </is>
       </c>
       <c r="G6" s="5" t="n">
-        <v>1.94</v>
+        <v>2.31</v>
       </c>
       <c r="H6" s="5" t="inlineStr"/>
       <c r="I6" s="5" t="inlineStr"/>
@@ -987,7 +987,7 @@
         </is>
       </c>
       <c r="G7" s="5" t="n">
-        <v>1.32</v>
+        <v>2</v>
       </c>
       <c r="H7" s="5" t="inlineStr"/>
       <c r="I7" s="5" t="inlineStr"/>
@@ -1024,7 +1024,7 @@
         </is>
       </c>
       <c r="G8" s="5" t="n">
-        <v>1.21</v>
+        <v>1.32</v>
       </c>
       <c r="H8" s="5" t="inlineStr"/>
       <c r="I8" s="5" t="inlineStr"/>
@@ -1061,7 +1061,7 @@
         </is>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="H9" s="5" t="inlineStr"/>
       <c r="I9" s="5" t="inlineStr"/>
@@ -1098,7 +1098,7 @@
         </is>
       </c>
       <c r="G10" s="5" t="n">
-        <v>1.12</v>
+        <v>1.24</v>
       </c>
       <c r="H10" s="5" t="inlineStr"/>
       <c r="I10" s="5" t="inlineStr"/>
@@ -1135,7 +1135,7 @@
         </is>
       </c>
       <c r="G11" s="5" t="n">
-        <v>6.3</v>
+        <v>0.91</v>
       </c>
       <c r="H11" s="5" t="inlineStr"/>
       <c r="I11" s="5" t="inlineStr"/>
@@ -1172,7 +1172,7 @@
         </is>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.99</v>
       </c>
       <c r="H12" s="5" t="inlineStr"/>
       <c r="I12" s="5" t="inlineStr"/>
@@ -1209,7 +1209,7 @@
         </is>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.72</v>
+        <v>1.08</v>
       </c>
       <c r="H13" s="5" t="inlineStr"/>
       <c r="I13" s="5" t="inlineStr"/>
@@ -1246,7 +1246,7 @@
         </is>
       </c>
       <c r="G14" s="5" t="n">
-        <v>1.04</v>
+        <v>0.91</v>
       </c>
       <c r="H14" s="5" t="inlineStr"/>
       <c r="I14" s="5" t="inlineStr"/>
@@ -1283,7 +1283,7 @@
         </is>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.59</v>
+        <v>0.71</v>
       </c>
       <c r="H15" s="5" t="inlineStr"/>
       <c r="I15" s="5" t="inlineStr"/>
@@ -1448,7 +1448,7 @@
         </is>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.84</v>
+        <v>1</v>
       </c>
       <c r="H20" s="5" t="inlineStr"/>
       <c r="I20" s="5" t="inlineStr"/>
@@ -1485,7 +1485,7 @@
         </is>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.71</v>
+        <v>0.91</v>
       </c>
       <c r="H21" s="5" t="inlineStr"/>
       <c r="I21" s="5" t="inlineStr"/>
@@ -1522,7 +1522,7 @@
         </is>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.96</v>
+        <v>1.06</v>
       </c>
       <c r="H22" s="5" t="inlineStr"/>
       <c r="I22" s="5" t="inlineStr"/>
@@ -1559,7 +1559,7 @@
         </is>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.11</v>
       </c>
       <c r="H23" s="5" t="inlineStr"/>
       <c r="I23" s="5" t="inlineStr"/>
@@ -1596,7 +1596,7 @@
         </is>
       </c>
       <c r="G24" s="5" t="n">
-        <v>1.36</v>
+        <v>1.51</v>
       </c>
       <c r="H24" s="5" t="inlineStr"/>
       <c r="I24" s="5" t="inlineStr"/>

--- a/docs/suivi-tests.xlsx
+++ b/docs/suivi-tests.xlsx
@@ -563,7 +563,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Dernier passage : 20/09/2026 18:01</t>
+          <t>Dernier passage : 20/09/2026 18:16</t>
         </is>
       </c>
     </row>
@@ -669,7 +669,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>82 joués</t>
+          <t>86 joués</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -876,7 +876,7 @@
         </is>
       </c>
       <c r="G4" s="5" t="n">
-        <v>1.16</v>
+        <v>1.08</v>
       </c>
       <c r="H4" s="5" t="inlineStr"/>
       <c r="I4" s="5" t="inlineStr"/>
@@ -913,7 +913,7 @@
         </is>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.64</v>
+        <v>0.51</v>
       </c>
       <c r="H5" s="5" t="inlineStr"/>
       <c r="I5" s="5" t="inlineStr"/>
@@ -950,7 +950,7 @@
         </is>
       </c>
       <c r="G6" s="5" t="n">
-        <v>2.31</v>
+        <v>2.46</v>
       </c>
       <c r="H6" s="5" t="inlineStr"/>
       <c r="I6" s="5" t="inlineStr"/>
@@ -987,7 +987,7 @@
         </is>
       </c>
       <c r="G7" s="5" t="n">
-        <v>2</v>
+        <v>1.59</v>
       </c>
       <c r="H7" s="5" t="inlineStr"/>
       <c r="I7" s="5" t="inlineStr"/>
@@ -1024,7 +1024,7 @@
         </is>
       </c>
       <c r="G8" s="5" t="n">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="H8" s="5" t="inlineStr"/>
       <c r="I8" s="5" t="inlineStr"/>
@@ -1061,7 +1061,7 @@
         </is>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.9</v>
+        <v>1.06</v>
       </c>
       <c r="H9" s="5" t="inlineStr"/>
       <c r="I9" s="5" t="inlineStr"/>
@@ -1098,7 +1098,7 @@
         </is>
       </c>
       <c r="G10" s="5" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="H10" s="5" t="inlineStr"/>
       <c r="I10" s="5" t="inlineStr"/>
@@ -1135,7 +1135,7 @@
         </is>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.91</v>
+        <v>6.47</v>
       </c>
       <c r="H11" s="5" t="inlineStr"/>
       <c r="I11" s="5" t="inlineStr"/>
@@ -1172,7 +1172,7 @@
         </is>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.99</v>
+        <v>1.05</v>
       </c>
       <c r="H12" s="5" t="inlineStr"/>
       <c r="I12" s="5" t="inlineStr"/>
@@ -1209,7 +1209,7 @@
         </is>
       </c>
       <c r="G13" s="5" t="n">
-        <v>1.08</v>
+        <v>0.84</v>
       </c>
       <c r="H13" s="5" t="inlineStr"/>
       <c r="I13" s="5" t="inlineStr"/>
@@ -1246,7 +1246,7 @@
         </is>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.91</v>
+        <v>0.8</v>
       </c>
       <c r="H14" s="5" t="inlineStr"/>
       <c r="I14" s="5" t="inlineStr"/>
@@ -1283,7 +1283,7 @@
         </is>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.71</v>
+        <v>0.62</v>
       </c>
       <c r="H15" s="5" t="inlineStr"/>
       <c r="I15" s="5" t="inlineStr"/>
@@ -1448,7 +1448,7 @@
         </is>
       </c>
       <c r="G20" s="5" t="n">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="H20" s="5" t="inlineStr"/>
       <c r="I20" s="5" t="inlineStr"/>
@@ -1485,7 +1485,7 @@
         </is>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.91</v>
+        <v>0.85</v>
       </c>
       <c r="H21" s="5" t="inlineStr"/>
       <c r="I21" s="5" t="inlineStr"/>
@@ -1522,7 +1522,7 @@
         </is>
       </c>
       <c r="G22" s="5" t="n">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="H22" s="5" t="inlineStr"/>
       <c r="I22" s="5" t="inlineStr"/>
@@ -1559,7 +1559,7 @@
         </is>
       </c>
       <c r="G23" s="5" t="n">
-        <v>1.11</v>
+        <v>1.02</v>
       </c>
       <c r="H23" s="5" t="inlineStr"/>
       <c r="I23" s="5" t="inlineStr"/>
@@ -1596,7 +1596,7 @@
         </is>
       </c>
       <c r="G24" s="5" t="n">
-        <v>1.51</v>
+        <v>1.57</v>
       </c>
       <c r="H24" s="5" t="inlineStr"/>
       <c r="I24" s="5" t="inlineStr"/>

--- a/docs/suivi-tests.xlsx
+++ b/docs/suivi-tests.xlsx
@@ -563,7 +563,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Dernier passage : 20/09/2026 18:16</t>
+          <t>Dernier passage : 20/09/2026 18:34</t>
         </is>
       </c>
     </row>
@@ -626,10 +626,10 @@
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="E6" s="5" t="n">
         <v>0</v>
@@ -642,11 +642,11 @@
       </c>
       <c r="H6" s="5" t="inlineStr">
         <is>
-          <t>22 / 70</t>
+          <t>25 / 70</t>
         </is>
       </c>
       <c r="I6" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -669,7 +669,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>86 joués</t>
+          <t>93 joués</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -776,7 +776,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I24"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -876,7 +876,7 @@
         </is>
       </c>
       <c r="G4" s="5" t="n">
-        <v>1.08</v>
+        <v>1.2</v>
       </c>
       <c r="H4" s="5" t="inlineStr"/>
       <c r="I4" s="5" t="inlineStr"/>
@@ -913,7 +913,7 @@
         </is>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.51</v>
+        <v>0.66</v>
       </c>
       <c r="H5" s="5" t="inlineStr"/>
       <c r="I5" s="5" t="inlineStr"/>
@@ -950,7 +950,7 @@
         </is>
       </c>
       <c r="G6" s="5" t="n">
-        <v>2.46</v>
+        <v>2</v>
       </c>
       <c r="H6" s="5" t="inlineStr"/>
       <c r="I6" s="5" t="inlineStr"/>
@@ -987,7 +987,7 @@
         </is>
       </c>
       <c r="G7" s="5" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="H7" s="5" t="inlineStr"/>
       <c r="I7" s="5" t="inlineStr"/>
@@ -1024,7 +1024,7 @@
         </is>
       </c>
       <c r="G8" s="5" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="H8" s="5" t="inlineStr"/>
       <c r="I8" s="5" t="inlineStr"/>
@@ -1061,7 +1061,7 @@
         </is>
       </c>
       <c r="G9" s="5" t="n">
-        <v>1.06</v>
+        <v>0.89</v>
       </c>
       <c r="H9" s="5" t="inlineStr"/>
       <c r="I9" s="5" t="inlineStr"/>
@@ -1098,7 +1098,7 @@
         </is>
       </c>
       <c r="G10" s="5" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="H10" s="5" t="inlineStr"/>
       <c r="I10" s="5" t="inlineStr"/>
@@ -1135,7 +1135,7 @@
         </is>
       </c>
       <c r="G11" s="5" t="n">
-        <v>6.47</v>
+        <v>0.82</v>
       </c>
       <c r="H11" s="5" t="inlineStr"/>
       <c r="I11" s="5" t="inlineStr"/>
@@ -1172,7 +1172,7 @@
         </is>
       </c>
       <c r="G12" s="5" t="n">
-        <v>1.05</v>
+        <v>0.91</v>
       </c>
       <c r="H12" s="5" t="inlineStr"/>
       <c r="I12" s="5" t="inlineStr"/>
@@ -1209,7 +1209,7 @@
         </is>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.84</v>
+        <v>0.89</v>
       </c>
       <c r="H13" s="5" t="inlineStr"/>
       <c r="I13" s="5" t="inlineStr"/>
@@ -1246,7 +1246,7 @@
         </is>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.8</v>
+        <v>0.77</v>
       </c>
       <c r="H14" s="5" t="inlineStr"/>
       <c r="I14" s="5" t="inlineStr"/>
@@ -1283,7 +1283,7 @@
         </is>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.62</v>
+        <v>0.61</v>
       </c>
       <c r="H15" s="5" t="inlineStr"/>
       <c r="I15" s="5" t="inlineStr"/>
@@ -1448,7 +1448,7 @@
         </is>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.96</v>
+        <v>0.82</v>
       </c>
       <c r="H20" s="5" t="inlineStr"/>
       <c r="I20" s="5" t="inlineStr"/>
@@ -1485,7 +1485,7 @@
         </is>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.85</v>
+        <v>0.77</v>
       </c>
       <c r="H21" s="5" t="inlineStr"/>
       <c r="I21" s="5" t="inlineStr"/>
@@ -1522,7 +1522,7 @@
         </is>
       </c>
       <c r="G22" s="5" t="n">
-        <v>1.13</v>
+        <v>1.01</v>
       </c>
       <c r="H22" s="5" t="inlineStr"/>
       <c r="I22" s="5" t="inlineStr"/>
@@ -1559,7 +1559,7 @@
         </is>
       </c>
       <c r="G23" s="5" t="n">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="H23" s="5" t="inlineStr"/>
       <c r="I23" s="5" t="inlineStr"/>
@@ -1596,13 +1596,198 @@
         </is>
       </c>
       <c r="G24" s="5" t="n">
-        <v>1.57</v>
+        <v>1.26</v>
       </c>
       <c r="H24" s="5" t="inlineStr"/>
       <c r="I24" s="5" t="inlineStr"/>
     </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>S22</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>Le gérant crée un compte depuis l'écran</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>Le compte est créé, retrouvé par la recherche, et la personne peut se connecter</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>C12</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>Automatisé</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>Vert</t>
+        </is>
+      </c>
+      <c r="G25" s="5" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="H25" s="5" t="inlineStr"/>
+      <c r="I25" s="5" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>S23</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>Une adresse déjà utilisée est refusée</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>Message lisible en français, formulaire conservé</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>C36</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>Automatisé</t>
+        </is>
+      </c>
+      <c r="F26" s="5" t="inlineStr">
+        <is>
+          <t>Vert</t>
+        </is>
+      </c>
+      <c r="G26" s="5" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="H26" s="5" t="inlineStr"/>
+      <c r="I26" s="5" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>S24</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>Les rôles proposés sont ceux que l'application sait attribuer</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>Ni parent ni comptable, qui n'ont pas encore d'application</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>C12c</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>Automatisé</t>
+        </is>
+      </c>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t>Vert</t>
+        </is>
+      </c>
+      <c r="G27" s="5" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="H27" s="5" t="inlineStr"/>
+      <c r="I27" s="5" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>S25</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>Le gérant exporte la liste du personnel</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>Le fichier se télécharge, en-têtes en français, sans colonne sensible</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>C33, C34</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>Automatisé</t>
+        </is>
+      </c>
+      <c r="F28" s="5" t="inlineStr">
+        <is>
+          <t>Vert</t>
+        </is>
+      </c>
+      <c r="G28" s="5" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="H28" s="5" t="inlineStr"/>
+      <c r="I28" s="5" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>S26</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>Le gérant retrouve un compte parmi des dizaines</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>La recherche et les filtres réduisent la liste ; réinitialiser la rend entière</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>C41</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>Automatisé</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
+          <t>Vert</t>
+        </is>
+      </c>
+      <c r="G29" s="5" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="H29" s="5" t="inlineStr"/>
+      <c r="I29" s="5" t="inlineStr"/>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="F4:F24">
+  <conditionalFormatting sqref="F4:F29">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"Vert"</formula>
     </cfRule>
@@ -1632,7 +1817,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E73"/>
+  <dimension ref="A1:E75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2389,15 +2574,15 @@
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>aucun parcours</t>
+          <t>S22 Le gérant crée un compte depuis l'écran</t>
         </is>
       </c>
       <c r="D32" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t>Filet technique seul</t>
+          <t>Vert</t>
         </is>
       </c>
     </row>
@@ -3114,15 +3299,15 @@
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>aucun parcours</t>
+          <t>S25 Le gérant exporte la liste du personnel</t>
         </is>
       </c>
       <c r="D61" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E61" s="5" t="inlineStr">
         <is>
-          <t>Filet technique seul</t>
+          <t>Vert</t>
         </is>
       </c>
     </row>
@@ -3189,15 +3374,15 @@
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>aucun parcours</t>
+          <t>S25 Le gérant exporte la liste du personnel</t>
         </is>
       </c>
       <c r="D64" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E64" s="5" t="inlineStr">
         <is>
-          <t>Filet technique seul</t>
+          <t>Vert</t>
         </is>
       </c>
     </row>
@@ -3239,11 +3424,11 @@
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>S02 Mot de passe erroné ; S06 Nom du club laissé vide</t>
+          <t>S02 Mot de passe erroné ; S06 Nom du club laissé vide ; S23 Une adresse déjà utilisée est refusée</t>
         </is>
       </c>
       <c r="D66" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E66" s="5" t="inlineStr">
         <is>
@@ -3423,6 +3608,56 @@
       <c r="E73" s="5" t="inlineStr">
         <is>
           <t>Filet technique seul</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="5" t="inlineStr">
+        <is>
+          <t>F01</t>
+        </is>
+      </c>
+      <c r="B74" s="5" t="inlineStr">
+        <is>
+          <t>C12c</t>
+        </is>
+      </c>
+      <c r="C74" s="5" t="inlineStr">
+        <is>
+          <t>S24 Les rôles proposés sont ceux que l'application sait attribuer</t>
+        </is>
+      </c>
+      <c r="D74" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E74" s="5" t="inlineStr">
+        <is>
+          <t>Hors fiche</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="5" t="inlineStr">
+        <is>
+          <t>F01</t>
+        </is>
+      </c>
+      <c r="B75" s="5" t="inlineStr">
+        <is>
+          <t>C41</t>
+        </is>
+      </c>
+      <c r="C75" s="5" t="inlineStr">
+        <is>
+          <t>S26 Le gérant retrouve un compte parmi des dizaines</t>
+        </is>
+      </c>
+      <c r="D75" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E75" s="5" t="inlineStr">
+        <is>
+          <t>Hors fiche</t>
         </is>
       </c>
     </row>
@@ -3430,7 +3665,7 @@
   <mergeCells count="1">
     <mergeCell ref="A1:E1"/>
   </mergeCells>
-  <conditionalFormatting sqref="E4:E73">
+  <conditionalFormatting sqref="E4:E75">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"Vert"</formula>
     </cfRule>
@@ -3460,7 +3695,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3629,12 +3864,12 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>À écrire</t>
+          <t>Test technique `ClubSeederTest.c42b`</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>Ouverte</t>
+          <t>Close</t>
         </is>
       </c>
     </row>
@@ -3838,32 +4073,64 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
+          <t>Un rôle sans aucun droit — le coach — tournait en boucle de redirections à la connexion</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>Recette S22</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>La personne croit s'être trompée et appelle le club ; rien ne lui dit ce qui se passe</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>S22</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>Close</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>F01</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
           <t>L'accueil détenait `users.exporter` sans `users.consulter` : un droit inopérant, qui s'activait dès qu'on lui accordait la simple lecture</t>
         </is>
       </c>
-      <c r="C14" s="5" t="inlineStr">
+      <c r="C15" s="5" t="inlineStr">
         <is>
           <t>Question soulevée par la recette S08, démontrée par l'API</t>
         </is>
       </c>
-      <c r="D14" s="5" t="inlineStr">
+      <c r="D15" s="5" t="inlineStr">
         <is>
           <t>Le gérant accorde « consulter la liste » et ouvre sans le savoir l'export de la liste du personnel, contre le critère C33b</t>
         </is>
       </c>
-      <c r="E14" s="5" t="inlineStr">
+      <c r="E15" s="5" t="inlineStr">
         <is>
           <t>Tests techniques `ExportsApiTest.c33c` et `ArchitectureTest.exporterSupposeConsulter`</t>
         </is>
       </c>
-      <c r="F14" s="5" t="inlineStr">
+      <c r="F15" s="5" t="inlineStr">
         <is>
           <t>Close</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="F4:F14">
+  <conditionalFormatting sqref="F4:F15">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"Close"</formula>
     </cfRule>

--- a/docs/suivi-tests.xlsx
+++ b/docs/suivi-tests.xlsx
@@ -44,7 +44,7 @@
       <sz val="13"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -81,6 +81,11 @@
         <fgColor rgb="00D8E4F0"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EDF1F5"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -108,7 +113,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -130,6 +135,12 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -563,7 +574,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Dernier passage : 20/09/2026 18:34</t>
+          <t>Dernier passage : 20/09/2026 18:49</t>
         </is>
       </c>
     </row>
@@ -626,10 +637,10 @@
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="E6" s="5" t="n">
         <v>0</v>
@@ -642,7 +653,7 @@
       </c>
       <c r="H6" s="5" t="inlineStr">
         <is>
-          <t>25 / 70</t>
+          <t>28 / 73</t>
         </is>
       </c>
       <c r="I6" s="5" t="n">
@@ -776,18 +787,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I29"/>
+  <dimension ref="A1:H49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
-    <col width="46" customWidth="1" min="2" max="2"/>
-    <col width="58" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="46" customWidth="1" min="4" max="4"/>
+    <col width="56" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
     <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="46" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -797,997 +807,1675 @@
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+    <row r="2" ht="28" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Chaque scénario se déroule tel qu'il est écrit : le préalable, les étapes, puis le résultat attendu. L'état vient du dernier passage, jamais d'une saisie.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>Scénario</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>Ce qu'on vérifie</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>Critères</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Préalable</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>Étapes</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>Résultat attendu</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>Mode</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr">
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t>État</t>
         </is>
       </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>Durée (s)</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
+      <c r="H4" s="4" t="inlineStr">
         <is>
           <t>Dernier passage</t>
         </is>
       </c>
-      <c r="I3" s="4" t="inlineStr">
-        <is>
-          <t>Détail</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>S01</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="inlineStr">
-        <is>
-          <t>Première connexion de l'administrateur</t>
-        </is>
-      </c>
-      <c r="C4" s="5" t="inlineStr">
-        <is>
-          <t>Mot de passe accepté, second facteur imposé avec QR et codes de secours, arrivée dans l'application</t>
-        </is>
-      </c>
-      <c r="D4" s="5" t="inlineStr">
-        <is>
-          <t>C5, C6b</t>
-        </is>
-      </c>
-      <c r="E4" s="5" t="inlineStr">
-        <is>
-          <t>Automatisé</t>
-        </is>
-      </c>
-      <c r="F4" s="5" t="inlineStr">
-        <is>
-          <t>Vert</t>
-        </is>
-      </c>
-      <c r="G4" s="5" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="H4" s="5" t="inlineStr"/>
-      <c r="I4" s="5" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>S02</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>Mot de passe erroné</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>Message lisible en français, aucun accès, aucune trace du mot de passe</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>C5, C36</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>Automatisé</t>
-        </is>
-      </c>
-      <c r="F5" s="5" t="inlineStr">
-        <is>
-          <t>Vert</t>
-        </is>
-      </c>
-      <c r="G5" s="5" t="n">
-        <v>0.66</v>
-      </c>
-      <c r="H5" s="5" t="inlineStr"/>
-      <c r="I5" s="5" t="inlineStr"/>
+      <c r="A5" s="13" t="inlineStr">
+        <is>
+          <t>Connexion et second facteur</t>
+        </is>
+      </c>
+      <c r="B5" s="14" t="n"/>
+      <c r="C5" s="14" t="n"/>
+      <c r="D5" s="14" t="n"/>
+      <c r="E5" s="14" t="n"/>
+      <c r="F5" s="14" t="n"/>
+      <c r="G5" s="14" t="n"/>
+      <c r="H5" s="14" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>S03</t>
+          <t>S01</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>Cinq échecs de suite verrouillent le compte</t>
+          <t>Première connexion</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>Le bon mot de passe est refusé pendant le verrouillage, avec un message qui le dit</t>
+          <t>un compte d'administration dont le second facteur n'est pas activé</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>C10b</t>
+          <t>1. Ouvrir l'application
+2. Saisir l'adresse électronique et le mot de passe
+3. Valider</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
+          <t>la session s'ouvre sur le premier écran que le rôle permet. L'en-tête nomme la personne connectée. La navigation ne montre que ce à quoi elle a droit.</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
           <t>Automatisé</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr">
-        <is>
-          <t>Vert</t>
-        </is>
-      </c>
-      <c r="G6" s="5" t="n">
-        <v>2</v>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>Vert</t>
+        </is>
       </c>
       <c r="H6" s="5" t="inlineStr"/>
-      <c r="I6" s="5" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>S04</t>
+          <t>S02</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>Connexion d'un compte déjà inscrit au second facteur</t>
+          <t>Mot de passe erroné</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>Le code est demandé ; ni QR ni nouveaux codes de secours ne sont produits</t>
+          <t>un compte existant</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>C6</t>
+          <t>1. Saisir la bonne adresse et un mauvais mot de passe
+2. Valider</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
+          <t>« Adresse électronique ou mot de passe incorrect. » On reste sur l'écran de connexion, et le mot de passe saisi n'apparaît nulle part.</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
           <t>Automatisé</t>
         </is>
       </c>
-      <c r="F7" s="5" t="inlineStr">
-        <is>
-          <t>Vert</t>
-        </is>
-      </c>
-      <c r="G7" s="5" t="n">
-        <v>1.57</v>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>Vert</t>
+        </is>
       </c>
       <c r="H7" s="5" t="inlineStr"/>
-      <c r="I7" s="5" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>S05</t>
+          <t>S03</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>Le gérant modifie l'identité du club</t>
+          <t>Cinq échecs verrouillent le compte</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>Le téléphone est normalisé en +212, la modification est visible au journal</t>
+          <t>un compte d'accueil jetable</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>C28, C37, C16</t>
+          <t>1. Saisir cinq fois de suite un mauvais mot de passe
+2. Saisir le bon mot de passe</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
+          <t>au sixième essai, même avec le bon mot de passe, l'accès est refusé avec « Compte bloqué après plusieurs échecs ». Le verrou tient quinze minutes.</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
           <t>Automatisé</t>
         </is>
       </c>
-      <c r="F8" s="5" t="inlineStr">
-        <is>
-          <t>Vert</t>
-        </is>
-      </c>
-      <c r="G8" s="5" t="n">
-        <v>1.36</v>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>Vert</t>
+        </is>
       </c>
       <c r="H8" s="5" t="inlineStr"/>
-      <c r="I8" s="5" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>S06</t>
+          <t>S04</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>Nom du club laissé vide</t>
+          <t>Connexion d'un compte déjà inscrit au second facteur</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>Refus avec un message en français, rien n'est enregistré</t>
+          <t>un compte de gérant dont le second facteur est activé</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>C36</t>
+          <t>1. Se connecter avec l'adresse et le mot de passe
+2. Saisir le code à six chiffres</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
+          <t>l'écran demande un code, sans afficher ni QR ni nouveaux codes de secours. La session s'ouvre, et aucun bandeau de rappel ne s'affiche : ce compte est protégé.</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
           <t>Automatisé</t>
         </is>
       </c>
-      <c r="F9" s="5" t="inlineStr">
-        <is>
-          <t>Vert</t>
-        </is>
-      </c>
-      <c r="G9" s="5" t="n">
-        <v>0.89</v>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>Vert</t>
+        </is>
       </c>
       <c r="H9" s="5" t="inlineStr"/>
-      <c r="I9" s="5" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>S07</t>
+          <t>S05</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>Consulter la liste des utilisateurs</t>
+          <t>Activer le second facteur depuis le bandeau</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>Rôle, second facteur, statut et dernière connexion lisibles, dates au fuseau du club</t>
+          <t>un compte de gérant sans second facteur</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>C29</t>
+          <t>1. Se connecter
+2. Cliquer « Activer maintenant » dans le bandeau
+3. Saisir le code produit par l'application d'authentification</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
+          <t>l'écran montre un QR et huit codes de secours. Après saisie du code, la session se poursuit sans ressaisir le mot de passe, et le bandeau disparaît.</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
           <t>Automatisé</t>
         </is>
       </c>
-      <c r="F10" s="5" t="inlineStr">
-        <is>
-          <t>Vert</t>
-        </is>
-      </c>
-      <c r="G10" s="5" t="n">
-        <v>1.29</v>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>Vert</t>
+        </is>
       </c>
       <c r="H10" s="5" t="inlineStr"/>
-      <c r="I10" s="5" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>S08</t>
+          <t>S06</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>L'accueil consulte sans modifier, et n'atteint pas le journal</t>
+          <t>Code de second facteur erroné</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>Champs en lecture seule, aucune action proposée, journal absent du menu et refusé par l'adresse directe</t>
+          <t>un compte dont le second facteur est activé</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>C11, C19, C32</t>
+          <t>1. Se connecter
+2. Saisir un code faux</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
+          <t>« Code incorrect. Vérifiez l'heure de votre téléphone, puis réessayez. » Le champ se vide, on reste sur l'écran.</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
           <t>Automatisé</t>
         </is>
       </c>
-      <c r="F11" s="5" t="inlineStr">
-        <is>
-          <t>Vert</t>
-        </is>
-      </c>
-      <c r="G11" s="5" t="n">
-        <v>0.82</v>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>Vert</t>
+        </is>
       </c>
       <c r="H11" s="5" t="inlineStr"/>
-      <c r="I11" s="5" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>S09</t>
+          <t>S07</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>Filtrer le journal d'audit</t>
+          <t>Se déconnecter</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>Le filtre par action réduit la liste ; la remise à zéro la rétablit</t>
+          <t>une session ouverte</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>C19b</t>
+          <t>1. Cliquer « Se déconnecter »
+2. Revenir en arrière dans le navigateur</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
+          <t>retour à l'écran de connexion, et le retour en arrière ne rouvre pas la session.</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
           <t>Automatisé</t>
         </is>
       </c>
-      <c r="F12" s="5" t="inlineStr">
-        <is>
-          <t>Vert</t>
-        </is>
-      </c>
-      <c r="G12" s="5" t="n">
-        <v>0.91</v>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>Vert</t>
+        </is>
       </c>
       <c r="H12" s="5" t="inlineStr"/>
-      <c r="I12" s="5" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>S10</t>
+          <t>S08</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>Se déconnecter</t>
+          <t>Recharger la page</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>Le retour en arrière ne rouvre pas la session</t>
+          <t>une session ouverte</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>C8</t>
+          <t>1. Recharger la page</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
+          <t>on reste dans l'application sans ressaisir le mot de passe. Le jeton d'accès n'a pas survécu au rechargement ; le cookie de renouvellement, si.</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
           <t>Automatisé</t>
         </is>
       </c>
-      <c r="F13" s="5" t="inlineStr">
-        <is>
-          <t>Vert</t>
-        </is>
-      </c>
-      <c r="G13" s="5" t="n">
-        <v>0.89</v>
+      <c r="G13" s="5" t="inlineStr">
+        <is>
+          <t>Vert</t>
+        </is>
       </c>
       <c r="H13" s="5" t="inlineStr"/>
-      <c r="I13" s="5" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>S11</t>
+          <t>S09</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>Recharger la page</t>
+          <t>L'accueil n'est jamais invitée à activer un second facteur</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>La session tient sans ressaisir le mot de passe, par le seul cookie</t>
+          <t>un compte d'accueil</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>C8c</t>
+          <t>1. Se connecter</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
+          <t>aucun bandeau de rappel. Il ne s'adresse qu'aux rôles qui ouvrent l'argent et les données sensibles.</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
           <t>Automatisé</t>
         </is>
       </c>
-      <c r="F14" s="5" t="inlineStr">
-        <is>
-          <t>Vert</t>
-        </is>
-      </c>
-      <c r="G14" s="5" t="n">
-        <v>0.77</v>
+      <c r="G14" s="5" t="inlineStr">
+        <is>
+          <t>Vert</t>
+        </is>
       </c>
       <c r="H14" s="5" t="inlineStr"/>
-      <c r="I14" s="5" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>Lire les règles configurables du club</t>
-        </is>
-      </c>
-      <c r="C15" s="5" t="inlineStr">
-        <is>
-          <t>Chaque règle affiche sa valeur, son origine et sa source documentée</t>
-        </is>
-      </c>
-      <c r="D15" s="5" t="inlineStr">
-        <is>
-          <t>C31</t>
-        </is>
-      </c>
-      <c r="E15" s="5" t="inlineStr">
-        <is>
-          <t>Automatisé</t>
-        </is>
-      </c>
-      <c r="F15" s="5" t="inlineStr">
-        <is>
-          <t>Vert</t>
-        </is>
-      </c>
-      <c r="G15" s="5" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="H15" s="5" t="inlineStr"/>
-      <c r="I15" s="5" t="inlineStr"/>
+      <c r="A15" s="13" t="inlineStr">
+        <is>
+          <t>Paramètres du club</t>
+        </is>
+      </c>
+      <c r="B15" s="14" t="n"/>
+      <c r="C15" s="14" t="n"/>
+      <c r="D15" s="14" t="n"/>
+      <c r="E15" s="14" t="n"/>
+      <c r="F15" s="14" t="n"/>
+      <c r="G15" s="14" t="n"/>
+      <c r="H15" s="14" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>S13</t>
+          <t>S10</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>Scanner le QR avec une vraie application d'authentification</t>
+          <t>Modifier l'identité du club</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>Le code produit par le téléphone est accepté</t>
+          <t>être connecté avec un droit de modification</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>C6</t>
+          <t>1. Ouvrir « Paramètres du club »
+2. Changer le nom
+3. Saisir le téléphone au format local, avec des espaces : 06 12 34 56 78
+4. Enregistrer
+5. Ouvrir le journal d'audit</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>Manuel</t>
+          <t>« Paramètres enregistrés. » Le téléphone s'affiche normalisé en +212612345678. Le journal porte une entrée club.updated, avec son auteur.</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>Manuel</t>
-        </is>
-      </c>
-      <c r="G16" s="5" t="n"/>
+          <t>Automatisé</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t>Vert</t>
+        </is>
+      </c>
       <c r="H16" s="5" t="inlineStr"/>
-      <c r="I16" s="5" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>S14</t>
+          <t>S11</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>Lire les écrans sur un téléphone, en portrait</t>
+          <t>Nom du club laissé vide</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>Rien n'est coupé, la navigation reste utilisable</t>
-        </is>
-      </c>
-      <c r="D17" s="5" t="inlineStr"/>
+          <t>être connecté avec un droit de modification</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>1. Vider le champ « Nom du club »
+2. Enregistrer
+3. Recharger la page</t>
+        </is>
+      </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>Manuel</t>
+          <t>« Le nom du club est obligatoire. » Rien n'est enregistré : le nom d'origine revient au rechargement.</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>Manuel</t>
-        </is>
-      </c>
-      <c r="G17" s="5" t="n"/>
+          <t>Automatisé</t>
+        </is>
+      </c>
+      <c r="G17" s="5" t="inlineStr">
+        <is>
+          <t>Vert</t>
+        </is>
+      </c>
       <c r="H17" s="5" t="inlineStr"/>
-      <c r="I17" s="5" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>S15</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>Valider les libellés FR avec l'accueil et le gérant</t>
+          <t>ICE mal formé</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>Le vocabulaire est celui du club, pas celui du logiciel</t>
-        </is>
-      </c>
-      <c r="D18" s="5" t="inlineStr"/>
+          <t>être connecté avec un droit de modification</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>1. Saisir 12345 dans le champ ICE
+2. Enregistrer</t>
+        </is>
+      </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>Manuel</t>
+          <t>« L'ICE compte quinze chiffres. » Rien n'est enregistré.</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>Manuel</t>
-        </is>
-      </c>
-      <c r="G18" s="5" t="n"/>
+          <t>Automatisé</t>
+        </is>
+      </c>
+      <c r="G18" s="5" t="inlineStr">
+        <is>
+          <t>Vert</t>
+        </is>
+      </c>
       <c r="H18" s="5" t="inlineStr"/>
-      <c r="I18" s="5" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>S16</t>
+          <t>S13</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>Imprimer la liste des utilisateurs</t>
+          <t>Changer la couleur du club</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>La feuille imprimée est lisible et tient sur la page</t>
-        </is>
-      </c>
-      <c r="D19" s="5" t="inlineStr"/>
+          <t>être connecté avec un droit de modification</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>1. Choisir une couleur principale
+2. Enregistrer
+3. Recharger la page</t>
+        </is>
+      </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>Manuel</t>
+          <t>l'accent de l'application prend la couleur choisie sans recharger, et elle est toujours là après rechargement.</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>Manuel</t>
-        </is>
-      </c>
-      <c r="G19" s="5" t="n"/>
+          <t>Automatisé</t>
+        </is>
+      </c>
+      <c r="G19" s="5" t="inlineStr">
+        <is>
+          <t>Vert</t>
+        </is>
+      </c>
       <c r="H19" s="5" t="inlineStr"/>
-      <c r="I19" s="5" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>S17</t>
+          <t>S14</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>Le gérant entre sans second facteur et voit un rappel permanent</t>
+          <t>Lire les règles configurables</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>Rien ne bloque, le rappel est sur chaque écran et ne se ferme pas</t>
+          <t>être connecté</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>C6g</t>
+          <t>1. Ouvrir « Paramètres du club »
+2. Descendre au tableau des règles</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
+          <t>chaque règle porte un libellé en français, une explication et sa valeur. L'origine dit « Défaut Clubify » ou « Choix du club ». Celles que le club ne peut pas changer portent « Fixée par Clubify » et n'ont pas de champ de saisie.</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
           <t>Automatisé</t>
         </is>
       </c>
-      <c r="F20" s="5" t="inlineStr">
-        <is>
-          <t>Vert</t>
-        </is>
-      </c>
-      <c r="G20" s="5" t="n">
-        <v>0.82</v>
+      <c r="G20" s="5" t="inlineStr">
+        <is>
+          <t>Vert</t>
+        </is>
       </c>
       <c r="H20" s="5" t="inlineStr"/>
-      <c r="I20" s="5" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>S18</t>
+          <t>S15</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>L'accueil n'est jamais invitée à activer un second facteur</t>
+          <t>Modifier une règle configurable</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>Le rappel ne s'adresse qu'aux rôles sensibles</t>
+          <t>être connecté avec un droit de modification</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>C6k</t>
+          <t>1. Porter « Durée d'un lien de fichier » à 25
+2. Enregistrer
+3. Recharger la page</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
+          <t>la valeur est retenue, et l'origine passe à « Choix du club ».</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
           <t>Automatisé</t>
         </is>
       </c>
-      <c r="F21" s="5" t="inlineStr">
-        <is>
-          <t>Vert</t>
-        </is>
-      </c>
-      <c r="G21" s="5" t="n">
-        <v>0.77</v>
+      <c r="G21" s="5" t="inlineStr">
+        <is>
+          <t>Vert</t>
+        </is>
       </c>
       <c r="H21" s="5" t="inlineStr"/>
-      <c r="I21" s="5" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>S19</t>
+          <t>S16</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>Le gérant change la couleur du club</t>
+          <t>Le nombre de lignes par page suit la règle du club</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>La couleur s'applique à l'écran dès l'enregistrement et survit au rechargement</t>
+          <t>être connecté avec un droit de modification, et plus de trente comptes dans le club</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>C28b</t>
+          <t>1. Porter « Lignes par page » à 30 dans les paramètres
+2. Enregistrer
+3. Se déconnecter, puis se reconnecter
+4. Ouvrir « Utilisateurs »</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
+          <t>la liste s'ouvre à trente lignes par page, sans qu'on ait rien choisi à l'écran.</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
           <t>Automatisé</t>
         </is>
       </c>
-      <c r="F22" s="5" t="inlineStr">
-        <is>
-          <t>Vert</t>
-        </is>
-      </c>
-      <c r="G22" s="5" t="n">
-        <v>1.01</v>
+      <c r="G22" s="5" t="inlineStr">
+        <is>
+          <t>Vert</t>
+        </is>
       </c>
       <c r="H22" s="5" t="inlineStr"/>
-      <c r="I22" s="5" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="inlineStr">
-        <is>
-          <t>S20</t>
-        </is>
-      </c>
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>Le gérant modifie une règle configurable</t>
-        </is>
-      </c>
-      <c r="C23" s="5" t="inlineStr">
-        <is>
-          <t>La valeur saisie est retenue, survit au rechargement, et l'origine passe à « choix du club »</t>
-        </is>
-      </c>
-      <c r="D23" s="5" t="inlineStr">
-        <is>
-          <t>C31b</t>
-        </is>
-      </c>
-      <c r="E23" s="5" t="inlineStr">
-        <is>
-          <t>Automatisé</t>
-        </is>
-      </c>
-      <c r="F23" s="5" t="inlineStr">
-        <is>
-          <t>Vert</t>
-        </is>
-      </c>
-      <c r="G23" s="5" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="H23" s="5" t="inlineStr"/>
-      <c r="I23" s="5" t="inlineStr"/>
+      <c r="A23" s="13" t="inlineStr">
+        <is>
+          <t>Utilisateurs</t>
+        </is>
+      </c>
+      <c r="B23" s="14" t="n"/>
+      <c r="C23" s="14" t="n"/>
+      <c r="D23" s="14" t="n"/>
+      <c r="E23" s="14" t="n"/>
+      <c r="F23" s="14" t="n"/>
+      <c r="G23" s="14" t="n"/>
+      <c r="H23" s="14" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>S21</t>
+          <t>S20</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>La liste des utilisateurs se parcourt page par page</t>
+          <t>Consulter la liste</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>La page s'ouvre à la taille retenue par le club, la plage affichée est juste, et changer la taille ramène au début</t>
+          <t>être connecté avec le droit de consulter</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>C40, C40c</t>
+          <t>1. Ouvrir « Utilisateurs »</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
+          <t>chaque ligne porte nom, adresse, rôle, état du second facteur, statut et dernière connexion. Les dates sont au fuseau du club. Un compte jamais connecté affiche « Jamais ».</t>
+        </is>
+      </c>
+      <c r="F24" s="5" t="inlineStr">
+        <is>
           <t>Automatisé</t>
         </is>
       </c>
-      <c r="F24" s="5" t="inlineStr">
-        <is>
-          <t>Vert</t>
-        </is>
-      </c>
-      <c r="G24" s="5" t="n">
-        <v>1.26</v>
+      <c r="G24" s="5" t="inlineStr">
+        <is>
+          <t>Vert</t>
+        </is>
       </c>
       <c r="H24" s="5" t="inlineStr"/>
-      <c r="I24" s="5" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>S22</t>
+          <t>S21</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>Le gérant crée un compte depuis l'écran</t>
+          <t>Parcourir la liste page par page</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>Le compte est créé, retrouvé par la recherche, et la personne peut se connecter</t>
+          <t>plus de vingt comptes dans le club</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>C12</t>
+          <t>1. Ouvrir « Utilisateurs »
+2. Lire la plage affichée
+3. Cliquer « Suivante »
+4. Cliquer « Précédente »</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
+          <t>la première page montre « 1–20 sur N ». « Suivante » montre « 21–40 sur N » avec des lignes différentes. « Précédente » ramène exactement à la première page.</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
           <t>Automatisé</t>
         </is>
       </c>
-      <c r="F25" s="5" t="inlineStr">
-        <is>
-          <t>Vert</t>
-        </is>
-      </c>
-      <c r="G25" s="5" t="n">
-        <v>1.41</v>
+      <c r="G25" s="5" t="inlineStr">
+        <is>
+          <t>Vert</t>
+        </is>
       </c>
       <c r="H25" s="5" t="inlineStr"/>
-      <c r="I25" s="5" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>S23</t>
+          <t>S22</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>Une adresse déjà utilisée est refusée</t>
+          <t>Changer le nombre de lignes par page</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>Message lisible en français, formulaire conservé</t>
+          <t>plus de trente comptes dans le club</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>C36</t>
+          <t>1. Aller à la deuxième page
+2. Choisir 50 lignes par page</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
+          <t>la liste revient à la première page et montre « 1–50 sur N ». Changer la taille ne laisse jamais sur une page qui n'existe plus.</t>
+        </is>
+      </c>
+      <c r="F26" s="5" t="inlineStr">
+        <is>
           <t>Automatisé</t>
         </is>
       </c>
-      <c r="F26" s="5" t="inlineStr">
-        <is>
-          <t>Vert</t>
-        </is>
-      </c>
-      <c r="G26" s="5" t="n">
-        <v>1.15</v>
+      <c r="G26" s="5" t="inlineStr">
+        <is>
+          <t>Vert</t>
+        </is>
       </c>
       <c r="H26" s="5" t="inlineStr"/>
-      <c r="I26" s="5" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>S24</t>
+          <t>S23</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>Les rôles proposés sont ceux que l'application sait attribuer</t>
+          <t>Chercher après avoir paginé</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>Ni parent ni comptable, qui n'ont pas encore d'application</t>
+          <t>plus de trente comptes, dont un compte connu créé pour l'occasion</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>C12c</t>
+          <t>1. Choisir 30 lignes par page
+2. Aller à la deuxième page
+3. Saisir l'adresse du compte connu dans la recherche</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
+          <t>la liste revient à la première page et ne montre qu'une seule ligne, celle du compte cherché. La plage affiche « 1–1 sur 1 » et les boutons de page sont inactifs.</t>
+        </is>
+      </c>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
           <t>Automatisé</t>
         </is>
       </c>
-      <c r="F27" s="5" t="inlineStr">
-        <is>
-          <t>Vert</t>
-        </is>
-      </c>
-      <c r="G27" s="5" t="n">
-        <v>0.78</v>
+      <c r="G27" s="5" t="inlineStr">
+        <is>
+          <t>Vert</t>
+        </is>
       </c>
       <c r="H27" s="5" t="inlineStr"/>
-      <c r="I27" s="5" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>S25</t>
+          <t>S24</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>Le gérant exporte la liste du personnel</t>
+          <t>Filtrer par rôle</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>Le fichier se télécharge, en-têtes en français, sans colonne sensible</t>
+          <t>des comptes de plusieurs rôles</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>C33, C34</t>
+          <t>1. Choisir « Coach » dans le filtre de rôle</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
+          <t>toutes les lignes affichées portent le rôle Coach, et le total change en conséquence.</t>
+        </is>
+      </c>
+      <c r="F28" s="5" t="inlineStr">
+        <is>
           <t>Automatisé</t>
         </is>
       </c>
-      <c r="F28" s="5" t="inlineStr">
-        <is>
-          <t>Vert</t>
-        </is>
-      </c>
-      <c r="G28" s="5" t="n">
-        <v>1.08</v>
+      <c r="G28" s="5" t="inlineStr">
+        <is>
+          <t>Vert</t>
+        </is>
       </c>
       <c r="H28" s="5" t="inlineStr"/>
-      <c r="I28" s="5" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
+          <t>S25</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>Filtrer par statut, puis réinitialiser</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>au moins un compte désactivé</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>1. Choisir « Désactivé » dans le filtre de statut
+2. Cliquer « Réinitialiser »</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>seules les lignes désactivées s'affichent, puis la liste entière revient et les filtres sont vides.</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
+          <t>Automatisé</t>
+        </is>
+      </c>
+      <c r="G29" s="5" t="inlineStr">
+        <is>
+          <t>Vert</t>
+        </is>
+      </c>
+      <c r="H29" s="5" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
           <t>S26</t>
         </is>
       </c>
-      <c r="B29" s="5" t="inlineStr">
-        <is>
-          <t>Le gérant retrouve un compte parmi des dizaines</t>
-        </is>
-      </c>
-      <c r="C29" s="5" t="inlineStr">
-        <is>
-          <t>La recherche et les filtres réduisent la liste ; réinitialiser la rend entière</t>
-        </is>
-      </c>
-      <c r="D29" s="5" t="inlineStr">
-        <is>
-          <t>C41</t>
-        </is>
-      </c>
-      <c r="E29" s="5" t="inlineStr">
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>Créer un compte</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>être connecté avec le droit de créer</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>1. Cliquer « Ajouter un utilisateur »
+2. Renseigner prénom, nom, adresse, rôle et mot de passe
+3. Créer le compte
+4. Chercher la nouvelle adresse dans la liste
+5. Se déconnecter et se connecter avec ce compte</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>« Compte créé. » Le compte se retrouve par la recherche, et la personne peut réellement se connecter.</t>
+        </is>
+      </c>
+      <c r="F30" s="5" t="inlineStr">
         <is>
           <t>Automatisé</t>
         </is>
       </c>
-      <c r="F29" s="5" t="inlineStr">
-        <is>
-          <t>Vert</t>
-        </is>
-      </c>
-      <c r="G29" s="5" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="H29" s="5" t="inlineStr"/>
-      <c r="I29" s="5" t="inlineStr"/>
+      <c r="G30" s="5" t="inlineStr">
+        <is>
+          <t>Vert</t>
+        </is>
+      </c>
+      <c r="H30" s="5" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>S27</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>Adresse déjà utilisée</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>un compte existant</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>1. Créer un compte avec une adresse déjà prise</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>« Cette adresse est déjà utilisée. » Le formulaire reste ouvert avec la saisie, rien n'est créé.</t>
+        </is>
+      </c>
+      <c r="F31" s="5" t="inlineStr">
+        <is>
+          <t>Automatisé</t>
+        </is>
+      </c>
+      <c r="G31" s="5" t="inlineStr">
+        <is>
+          <t>Vert</t>
+        </is>
+      </c>
+      <c r="H31" s="5" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>S28</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>Mot de passe trop court</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>être connecté avec le droit de créer</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="inlineStr">
+        <is>
+          <t>1. Créer un compte avec un mot de passe de onze caractères</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t>le compte n'est pas créé, et le message dit que le mot de passe est trop court.</t>
+        </is>
+      </c>
+      <c r="F32" s="5" t="inlineStr">
+        <is>
+          <t>Automatisé</t>
+        </is>
+      </c>
+      <c r="G32" s="5" t="inlineStr">
+        <is>
+          <t>Vert</t>
+        </is>
+      </c>
+      <c r="H32" s="5" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>S29</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>Les rôles proposés sont ceux que l'application sait attribuer</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>être connecté avec le droit de créer</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>1. Ouvrir le formulaire de création
+2. Dérouler la liste des rôles</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>Administrateur, Gérant, Accueil et Coach. Ni Parent ni Comptable : leur application n'existe pas encore, les proposer serait un piège.</t>
+        </is>
+      </c>
+      <c r="F33" s="5" t="inlineStr">
+        <is>
+          <t>Automatisé</t>
+        </is>
+      </c>
+      <c r="G33" s="5" t="inlineStr">
+        <is>
+          <t>Vert</t>
+        </is>
+      </c>
+      <c r="H33" s="5" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>S30</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>Exporter la liste du personnel</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>être connecté avec le droit d'exporter</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t>1. Cliquer « Exporter »</t>
+        </is>
+      </c>
+      <c r="E34" s="5" t="inlineStr">
+        <is>
+          <t>un fichier utilisateurs.csv se télécharge, en-têtes en français, contenant les comptes. Aucune colonne sensible n'y figure.</t>
+        </is>
+      </c>
+      <c r="F34" s="5" t="inlineStr">
+        <is>
+          <t>Automatisé</t>
+        </is>
+      </c>
+      <c r="G34" s="5" t="inlineStr">
+        <is>
+          <t>Vert</t>
+        </is>
+      </c>
+      <c r="H34" s="5" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>S31</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>Un rôle sans écran le sait</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>un compte de coach</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>1. Se connecter avec ce compte</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>« Votre espace n'est pas encore ouvert. » Pas de page blanche, pas de renvoi d'un écran à l'autre.</t>
+        </is>
+      </c>
+      <c r="F35" s="5" t="inlineStr">
+        <is>
+          <t>Automatisé</t>
+        </is>
+      </c>
+      <c r="G35" s="5" t="inlineStr">
+        <is>
+          <t>Vert</t>
+        </is>
+      </c>
+      <c r="H35" s="5" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="13" t="inlineStr">
+        <is>
+          <t>Journal d'audit</t>
+        </is>
+      </c>
+      <c r="B36" s="14" t="n"/>
+      <c r="C36" s="14" t="n"/>
+      <c r="D36" s="14" t="n"/>
+      <c r="E36" s="14" t="n"/>
+      <c r="F36" s="14" t="n"/>
+      <c r="G36" s="14" t="n"/>
+      <c r="H36" s="14" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>S40</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>Consulter le journal</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>être connecté avec le droit de consulter le journal</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>1. Ouvrir « Journal d'audit »</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>les entrées les plus récentes d'abord, avec horodatage au fuseau du club, auteur, type, action et cible. Une connexion réussie porte l'adresse de la personne, jamais « Système ».</t>
+        </is>
+      </c>
+      <c r="F37" s="5" t="inlineStr">
+        <is>
+          <t>Automatisé</t>
+        </is>
+      </c>
+      <c r="G37" s="5" t="inlineStr">
+        <is>
+          <t>Vert</t>
+        </is>
+      </c>
+      <c r="H37" s="5" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>S41</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>Filtrer le journal par action</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>des entrées de plusieurs actions</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="inlineStr">
+        <is>
+          <t>1. Saisir auth.login.succeeded dans le filtre d'action
+2. Filtrer
+3. Réinitialiser</t>
+        </is>
+      </c>
+      <c r="E38" s="5" t="inlineStr">
+        <is>
+          <t>toutes les lignes affichées portent cette action, sans exception. Réinitialiser vide le filtre et rend la liste entière.</t>
+        </is>
+      </c>
+      <c r="F38" s="5" t="inlineStr">
+        <is>
+          <t>Automatisé</t>
+        </is>
+      </c>
+      <c r="G38" s="5" t="inlineStr">
+        <is>
+          <t>Vert</t>
+        </is>
+      </c>
+      <c r="H38" s="5" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>S42</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>Filtrer le journal par période</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>être connecté avec le droit de consulter le journal</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="inlineStr">
+        <is>
+          <t>1. Choisir comme date de début le lendemain
+2. Filtrer</t>
+        </is>
+      </c>
+      <c r="E39" s="5" t="inlineStr">
+        <is>
+          <t>aucune entrée, et le tableau le dit : « Aucune entrée pour ces critères. » Pas de page vide sans explication.</t>
+        </is>
+      </c>
+      <c r="F39" s="5" t="inlineStr">
+        <is>
+          <t>Automatisé</t>
+        </is>
+      </c>
+      <c r="G39" s="5" t="inlineStr">
+        <is>
+          <t>Vert</t>
+        </is>
+      </c>
+      <c r="H39" s="5" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>S43</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="inlineStr">
+        <is>
+          <t>Parcourir le journal page par page</t>
+        </is>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>plus d'une page d'entrées</t>
+        </is>
+      </c>
+      <c r="D40" s="5" t="inlineStr">
+        <is>
+          <t>1. Ouvrir le journal
+2. Cliquer « Suivante »</t>
+        </is>
+      </c>
+      <c r="E40" s="5" t="inlineStr">
+        <is>
+          <t>la page change et les entrées sont différentes. Le journal est borné comme les autres listes.</t>
+        </is>
+      </c>
+      <c r="F40" s="5" t="inlineStr">
+        <is>
+          <t>Automatisé</t>
+        </is>
+      </c>
+      <c r="G40" s="5" t="inlineStr">
+        <is>
+          <t>Vert</t>
+        </is>
+      </c>
+      <c r="H40" s="5" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="13" t="inlineStr">
+        <is>
+          <t>Droits et accès</t>
+        </is>
+      </c>
+      <c r="B41" s="14" t="n"/>
+      <c r="C41" s="14" t="n"/>
+      <c r="D41" s="14" t="n"/>
+      <c r="E41" s="14" t="n"/>
+      <c r="F41" s="14" t="n"/>
+      <c r="G41" s="14" t="n"/>
+      <c r="H41" s="14" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>S50</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>L'accueil consulte les paramètres sans pouvoir les modifier</t>
+        </is>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>un compte d'accueil</t>
+        </is>
+      </c>
+      <c r="D42" s="5" t="inlineStr">
+        <is>
+          <t>1. Se connecter
+2. Ouvrir « Paramètres du club »</t>
+        </is>
+      </c>
+      <c r="E42" s="5" t="inlineStr">
+        <is>
+          <t>les champs se lisent mais ne se saisissent pas, aucun bouton « Enregistrer », et les règles configurables n'ont pas de champ.</t>
+        </is>
+      </c>
+      <c r="F42" s="5" t="inlineStr">
+        <is>
+          <t>Automatisé</t>
+        </is>
+      </c>
+      <c r="G42" s="5" t="inlineStr">
+        <is>
+          <t>Vert</t>
+        </is>
+      </c>
+      <c r="H42" s="5" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>S51</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>L'accueil n'atteint pas le journal, même par l'adresse</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>un compte d'accueil</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="inlineStr">
+        <is>
+          <t>1. Se connecter
+2. Constater que « Journal d'audit » est absent du menu
+3. Saisir l'adresse du journal à la main dans le navigateur</t>
+        </is>
+      </c>
+      <c r="E43" s="5" t="inlineStr">
+        <is>
+          <t>le journal ne s'ouvre pas, et l'accueil est renvoyée vers un écran qui lui est permis.</t>
+        </is>
+      </c>
+      <c r="F43" s="5" t="inlineStr">
+        <is>
+          <t>Automatisé</t>
+        </is>
+      </c>
+      <c r="G43" s="5" t="inlineStr">
+        <is>
+          <t>Vert</t>
+        </is>
+      </c>
+      <c r="H43" s="5" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t>S52</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>L'accueil ne voit pas la liste du personnel</t>
+        </is>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>un compte d'accueil</t>
+        </is>
+      </c>
+      <c r="D44" s="5" t="inlineStr">
+        <is>
+          <t>1. Se connecter
+2. Regarder le menu</t>
+        </is>
+      </c>
+      <c r="E44" s="5" t="inlineStr">
+        <is>
+          <t>« Utilisateurs » est absent. Le menu ne promet que ce que le droit permet.</t>
+        </is>
+      </c>
+      <c r="F44" s="5" t="inlineStr">
+        <is>
+          <t>Automatisé</t>
+        </is>
+      </c>
+      <c r="G44" s="5" t="inlineStr">
+        <is>
+          <t>Vert</t>
+        </is>
+      </c>
+      <c r="H44" s="5" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="13" t="inlineStr">
+        <is>
+          <t>Recette manuelle</t>
+        </is>
+      </c>
+      <c r="B45" s="14" t="n"/>
+      <c r="C45" s="14" t="n"/>
+      <c r="D45" s="14" t="n"/>
+      <c r="E45" s="14" t="n"/>
+      <c r="F45" s="14" t="n"/>
+      <c r="G45" s="14" t="n"/>
+      <c r="H45" s="14" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>S90</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="inlineStr">
+        <is>
+          <t>Scanner le QR avec un vrai téléphone</t>
+        </is>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>un compte de gérant sans second facteur, un téléphone avec une application d'authentification</t>
+        </is>
+      </c>
+      <c r="D46" s="5" t="inlineStr">
+        <is>
+          <t>1. Se connecter, cliquer « Activer maintenant »
+2. Scanner le code avec le téléphone
+3. Noter les codes de secours
+4. Saisir le code à six chiffres</t>
+        </is>
+      </c>
+      <c r="E46" s="5" t="inlineStr">
+        <is>
+          <t>le téléphone reconnaît le compte sous le nom du club, et le code produit est accepté. Aucune machine ne peut jouer ce scénario.</t>
+        </is>
+      </c>
+      <c r="F46" s="5" t="inlineStr">
+        <is>
+          <t>Manuel</t>
+        </is>
+      </c>
+      <c r="G46" s="5" t="inlineStr">
+        <is>
+          <t>Manuel</t>
+        </is>
+      </c>
+      <c r="H46" s="5" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t>S91</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>Lire les écrans sur un téléphone, en portrait</t>
+        </is>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>un téléphone</t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="inlineStr">
+        <is>
+          <t>1. Ouvrir l'application sur le téléphone
+2. Parcourir connexion, paramètres du club, utilisateurs et journal</t>
+        </is>
+      </c>
+      <c r="E47" s="5" t="inlineStr">
+        <is>
+          <t>rien n'est coupé, les tableaux se font défiler, les boutons restent atteignables au pouce.</t>
+        </is>
+      </c>
+      <c r="F47" s="5" t="inlineStr">
+        <is>
+          <t>Manuel</t>
+        </is>
+      </c>
+      <c r="G47" s="5" t="inlineStr">
+        <is>
+          <t>Manuel</t>
+        </is>
+      </c>
+      <c r="H47" s="5" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="5" t="inlineStr">
+        <is>
+          <t>S92</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="inlineStr">
+        <is>
+          <t>Valider les libellés avec l'accueil et le gérant</t>
+        </is>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>l'accueil et le gérant devant l'écran</t>
+        </is>
+      </c>
+      <c r="D48" s="5" t="inlineStr">
+        <is>
+          <t>1. Parcourir chaque écran avec eux
+2. Relever chaque mot qui ne leur parle pas</t>
+        </is>
+      </c>
+      <c r="E48" s="5" t="inlineStr">
+        <is>
+          <t>le vocabulaire est celui du club, pas celui du logiciel. Tout écart est noté et corrigé.</t>
+        </is>
+      </c>
+      <c r="F48" s="5" t="inlineStr">
+        <is>
+          <t>Manuel</t>
+        </is>
+      </c>
+      <c r="G48" s="5" t="inlineStr">
+        <is>
+          <t>Manuel</t>
+        </is>
+      </c>
+      <c r="H48" s="5" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>S93</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="inlineStr">
+        <is>
+          <t>Imprimer la liste des utilisateurs</t>
+        </is>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>une liste à l'écran</t>
+        </is>
+      </c>
+      <c r="D49" s="5" t="inlineStr">
+        <is>
+          <t>1. Imprimer depuis le navigateur</t>
+        </is>
+      </c>
+      <c r="E49" s="5" t="inlineStr">
+        <is>
+          <t>la feuille est lisible, tient dans la largeur, et ne coupe pas les colonnes.</t>
+        </is>
+      </c>
+      <c r="F49" s="5" t="inlineStr">
+        <is>
+          <t>Manuel</t>
+        </is>
+      </c>
+      <c r="G49" s="5" t="inlineStr">
+        <is>
+          <t>Manuel</t>
+        </is>
+      </c>
+      <c r="H49" s="5" t="inlineStr"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="F4:F29">
+  <mergeCells count="1">
+    <mergeCell ref="A2:H2"/>
+  </mergeCells>
+  <conditionalFormatting sqref="G5:G49">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"Vert"</formula>
     </cfRule>
@@ -1817,7 +2505,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E75"/>
+  <dimension ref="A1:E76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1974,7 +2662,7 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>S01 Première connexion de l'administrateur ; S02 Mot de passe erroné</t>
+          <t>S01 Première connexion ; S02 Mot de passe erroné</t>
         </is>
       </c>
       <c r="D8" s="5" t="n">
@@ -1999,15 +2687,15 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>aucun parcours</t>
+          <t>S28 Mot de passe trop court</t>
         </is>
       </c>
       <c r="D9" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>Filet technique seul</t>
+          <t>Vert</t>
         </is>
       </c>
     </row>
@@ -2024,11 +2712,11 @@
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>S04 Connexion d'un compte déjà inscrit au second facteur ; S13 Scanner le QR avec une vraie application d'authentification</t>
+          <t>S04 Connexion d'un compte déjà inscrit au second facteur ; S06 Code de second facteur erroné ; S90 Scanner le QR avec un vrai téléphone</t>
         </is>
       </c>
       <c r="D10" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
@@ -2049,7 +2737,7 @@
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>S01 Première connexion de l'administrateur</t>
+          <t>S05 Activer le second facteur depuis le bandeau</t>
         </is>
       </c>
       <c r="D11" s="5" t="n">
@@ -2174,7 +2862,7 @@
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>S17 Le gérant entre sans second facteur et voit un rappel permanent</t>
+          <t>S05 Activer le second facteur depuis le bandeau</t>
         </is>
       </c>
       <c r="D16" s="5" t="n">
@@ -2274,7 +2962,7 @@
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>S18 L'accueil n'est jamais invitée à activer un second facteur</t>
+          <t>S09 L'accueil n'est jamais invitée à activer un second facteur</t>
         </is>
       </c>
       <c r="D20" s="5" t="n">
@@ -2324,7 +3012,7 @@
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>S10 Se déconnecter</t>
+          <t>S07 Se déconnecter</t>
         </is>
       </c>
       <c r="D22" s="5" t="n">
@@ -2374,7 +3062,7 @@
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>S11 Recharger la page</t>
+          <t>S08 Recharger la page</t>
         </is>
       </c>
       <c r="D24" s="5" t="n">
@@ -2449,7 +3137,7 @@
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>S03 Cinq échecs de suite verrouillent le compte</t>
+          <t>S03 Cinq échecs verrouillent le compte</t>
         </is>
       </c>
       <c r="D27" s="5" t="n">
@@ -2474,11 +3162,11 @@
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>S08 L'accueil consulte sans modifier, et n'atteint pas le journal</t>
+          <t>S50 L'accueil consulte les paramètres sans pouvoir les modifier ; S52 L'accueil ne voit pas la liste du personnel</t>
         </is>
       </c>
       <c r="D28" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
@@ -2574,11 +3262,11 @@
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>S22 Le gérant crée un compte depuis l'écran</t>
+          <t>S26 Créer un compte ; S31 Un rôle sans écran le sait</t>
         </is>
       </c>
       <c r="D32" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
@@ -2644,20 +3332,20 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>C13</t>
+          <t>C12c</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>aucun parcours</t>
+          <t>S29 Les rôles proposés sont ceux que l'application sait attribuer</t>
         </is>
       </c>
       <c r="D35" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t>Filet technique seul</t>
+          <t>Vert</t>
         </is>
       </c>
     </row>
@@ -2669,7 +3357,7 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>C14</t>
+          <t>C13</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
@@ -2694,7 +3382,7 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>C15</t>
+          <t>C14</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
@@ -2719,20 +3407,20 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>C16</t>
+          <t>C15</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>S05 Le gérant modifie l'identité du club</t>
+          <t>aucun parcours</t>
         </is>
       </c>
       <c r="D38" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
-          <t>Vert</t>
+          <t>Filet technique seul</t>
         </is>
       </c>
     </row>
@@ -2744,20 +3432,20 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>C16b</t>
+          <t>C16</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>aucun parcours</t>
+          <t>S10 Modifier l'identité du club</t>
         </is>
       </c>
       <c r="D39" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t>Filet technique seul</t>
+          <t>Vert</t>
         </is>
       </c>
     </row>
@@ -2769,7 +3457,7 @@
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>C16c</t>
+          <t>C16b</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
@@ -2794,7 +3482,7 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>C17</t>
+          <t>C16c</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
@@ -2819,7 +3507,7 @@
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>C18</t>
+          <t>C17</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
@@ -2844,20 +3532,20 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>C19</t>
+          <t>C18</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>S08 L'accueil consulte sans modifier, et n'atteint pas le journal</t>
+          <t>aucun parcours</t>
         </is>
       </c>
       <c r="D43" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
-          <t>Vert</t>
+          <t>Filet technique seul</t>
         </is>
       </c>
     </row>
@@ -2869,16 +3557,16 @@
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>C19b</t>
+          <t>C19</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>S09 Filtrer le journal d'audit</t>
+          <t>S40 Consulter le journal ; S51 L'accueil n'atteint pas le journal, même par l'adresse</t>
         </is>
       </c>
       <c r="D44" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E44" s="5" t="inlineStr">
         <is>
@@ -2894,20 +3582,20 @@
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>C20</t>
+          <t>C19b</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>aucun parcours</t>
+          <t>S41 Filtrer le journal par action ; S42 Filtrer le journal par période ; S43 Parcourir le journal page par page</t>
         </is>
       </c>
       <c r="D45" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E45" s="5" t="inlineStr">
         <is>
-          <t>Filet technique seul</t>
+          <t>Vert</t>
         </is>
       </c>
     </row>
@@ -2919,7 +3607,7 @@
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>C21</t>
+          <t>C20</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
@@ -2944,7 +3632,7 @@
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>C22</t>
+          <t>C21</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
@@ -2969,7 +3657,7 @@
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>C22b</t>
+          <t>C22</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
@@ -2994,7 +3682,7 @@
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>C23</t>
+          <t>C22b</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
@@ -3019,7 +3707,7 @@
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>C24</t>
+          <t>C23</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
@@ -3044,7 +3732,7 @@
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>C25</t>
+          <t>C24</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
@@ -3069,7 +3757,7 @@
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>C26</t>
+          <t>C25</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
@@ -3094,7 +3782,7 @@
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>C27</t>
+          <t>C26</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
@@ -3119,20 +3807,20 @@
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>C28</t>
+          <t>C27</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>S05 Le gérant modifie l'identité du club</t>
+          <t>aucun parcours</t>
         </is>
       </c>
       <c r="D54" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E54" s="5" t="inlineStr">
         <is>
-          <t>Vert</t>
+          <t>Filet technique seul</t>
         </is>
       </c>
     </row>
@@ -3144,16 +3832,16 @@
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>C28b</t>
+          <t>C28</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>S19 Le gérant change la couleur du club</t>
+          <t>S10 Modifier l'identité du club ; S12 ICE mal formé</t>
         </is>
       </c>
       <c r="D55" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E55" s="5" t="inlineStr">
         <is>
@@ -3169,12 +3857,12 @@
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>C29</t>
+          <t>C28b</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>S07 Consulter la liste des utilisateurs</t>
+          <t>S13 Changer la couleur du club</t>
         </is>
       </c>
       <c r="D56" s="5" t="n">
@@ -3194,20 +3882,20 @@
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>C30</t>
+          <t>C29</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>aucun parcours</t>
+          <t>S20 Consulter la liste</t>
         </is>
       </c>
       <c r="D57" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E57" s="5" t="inlineStr">
         <is>
-          <t>Filet technique seul</t>
+          <t>Vert</t>
         </is>
       </c>
     </row>
@@ -3219,20 +3907,20 @@
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>C31</t>
+          <t>C30</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>S12 Lire les règles configurables du club</t>
+          <t>aucun parcours</t>
         </is>
       </c>
       <c r="D58" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E58" s="5" t="inlineStr">
         <is>
-          <t>Vert</t>
+          <t>Filet technique seul</t>
         </is>
       </c>
     </row>
@@ -3244,12 +3932,12 @@
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>C31b</t>
+          <t>C31</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>S20 Le gérant modifie une règle configurable</t>
+          <t>S14 Lire les règles configurables</t>
         </is>
       </c>
       <c r="D59" s="5" t="n">
@@ -3269,12 +3957,12 @@
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>C32</t>
+          <t>C31b</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>S08 L'accueil consulte sans modifier, et n'atteint pas le journal</t>
+          <t>S15 Modifier une règle configurable</t>
         </is>
       </c>
       <c r="D60" s="5" t="n">
@@ -3294,12 +3982,12 @@
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>C33</t>
+          <t>C32</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>S25 Le gérant exporte la liste du personnel</t>
+          <t>S50 L'accueil consulte les paramètres sans pouvoir les modifier</t>
         </is>
       </c>
       <c r="D61" s="5" t="n">
@@ -3319,20 +4007,20 @@
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>C33b</t>
+          <t>C33</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>aucun parcours</t>
+          <t>S30 Exporter la liste du personnel</t>
         </is>
       </c>
       <c r="D62" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E62" s="5" t="inlineStr">
         <is>
-          <t>Filet technique seul</t>
+          <t>Vert</t>
         </is>
       </c>
     </row>
@@ -3344,7 +4032,7 @@
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>C33c</t>
+          <t>C33b</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
@@ -3369,20 +4057,20 @@
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>C34</t>
+          <t>C33c</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>S25 Le gérant exporte la liste du personnel</t>
+          <t>aucun parcours</t>
         </is>
       </c>
       <c r="D64" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E64" s="5" t="inlineStr">
         <is>
-          <t>Vert</t>
+          <t>Filet technique seul</t>
         </is>
       </c>
     </row>
@@ -3394,20 +4082,20 @@
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>C35</t>
+          <t>C34</t>
         </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>aucun parcours</t>
+          <t>S30 Exporter la liste du personnel</t>
         </is>
       </c>
       <c r="D65" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E65" s="5" t="inlineStr">
         <is>
-          <t>Filet technique seul</t>
+          <t>Vert</t>
         </is>
       </c>
     </row>
@@ -3419,20 +4107,20 @@
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>C36</t>
+          <t>C35</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>S02 Mot de passe erroné ; S06 Nom du club laissé vide ; S23 Une adresse déjà utilisée est refusée</t>
+          <t>aucun parcours</t>
         </is>
       </c>
       <c r="D66" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E66" s="5" t="inlineStr">
         <is>
-          <t>Vert</t>
+          <t>Filet technique seul</t>
         </is>
       </c>
     </row>
@@ -3444,16 +4132,16 @@
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>C37</t>
+          <t>C36</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>S05 Le gérant modifie l'identité du club</t>
+          <t>S02 Mot de passe erroné ; S06 Code de second facteur erroné ; S11 Nom du club laissé vide ; S27 Adresse déjà utilisée</t>
         </is>
       </c>
       <c r="D67" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E67" s="5" t="inlineStr">
         <is>
@@ -3469,20 +4157,20 @@
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>C38</t>
+          <t>C37</t>
         </is>
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>aucun parcours</t>
+          <t>S10 Modifier l'identité du club</t>
         </is>
       </c>
       <c r="D68" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E68" s="5" t="inlineStr">
         <is>
-          <t>Filet technique seul</t>
+          <t>Vert</t>
         </is>
       </c>
     </row>
@@ -3494,7 +4182,7 @@
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>C39</t>
+          <t>C38</t>
         </is>
       </c>
       <c r="C69" s="5" t="inlineStr">
@@ -3519,20 +4207,20 @@
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
-          <t>C40</t>
+          <t>C39</t>
         </is>
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>S21 La liste des utilisateurs se parcourt page par page</t>
+          <t>aucun parcours</t>
         </is>
       </c>
       <c r="D70" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E70" s="5" t="inlineStr">
         <is>
-          <t>Vert</t>
+          <t>Filet technique seul</t>
         </is>
       </c>
     </row>
@@ -3544,20 +4232,20 @@
       </c>
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>C40b</t>
+          <t>C40</t>
         </is>
       </c>
       <c r="C71" s="5" t="inlineStr">
         <is>
-          <t>aucun parcours</t>
+          <t>S21 Parcourir la liste page par page ; S22 Changer le nombre de lignes par page ; S23 Chercher après avoir paginé ; S43 Parcourir le journal page par page</t>
         </is>
       </c>
       <c r="D71" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E71" s="5" t="inlineStr">
         <is>
-          <t>Filet technique seul</t>
+          <t>Vert</t>
         </is>
       </c>
     </row>
@@ -3569,20 +4257,20 @@
       </c>
       <c r="B72" s="5" t="inlineStr">
         <is>
-          <t>C40c</t>
+          <t>C40b</t>
         </is>
       </c>
       <c r="C72" s="5" t="inlineStr">
         <is>
-          <t>S21 La liste des utilisateurs se parcourt page par page</t>
+          <t>aucun parcours</t>
         </is>
       </c>
       <c r="D72" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E72" s="5" t="inlineStr">
         <is>
-          <t>Vert</t>
+          <t>Filet technique seul</t>
         </is>
       </c>
     </row>
@@ -3594,20 +4282,20 @@
       </c>
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>C40d</t>
+          <t>C40c</t>
         </is>
       </c>
       <c r="C73" s="5" t="inlineStr">
         <is>
-          <t>aucun parcours</t>
+          <t>S16 Le nombre de lignes par page suit la règle du club</t>
         </is>
       </c>
       <c r="D73" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E73" s="5" t="inlineStr">
         <is>
-          <t>Filet technique seul</t>
+          <t>Vert</t>
         </is>
       </c>
     </row>
@@ -3619,20 +4307,20 @@
       </c>
       <c r="B74" s="5" t="inlineStr">
         <is>
-          <t>C12c</t>
+          <t>C40d</t>
         </is>
       </c>
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t>S24 Les rôles proposés sont ceux que l'application sait attribuer</t>
+          <t>aucun parcours</t>
         </is>
       </c>
       <c r="D74" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E74" s="5" t="inlineStr">
         <is>
-          <t>Hors fiche</t>
+          <t>Filet technique seul</t>
         </is>
       </c>
     </row>
@@ -3649,15 +4337,40 @@
       </c>
       <c r="C75" s="5" t="inlineStr">
         <is>
-          <t>S26 Le gérant retrouve un compte parmi des dizaines</t>
+          <t>S23 Chercher après avoir paginé ; S24 Filtrer par rôle ; S25 Filtrer par statut, puis réinitialiser</t>
         </is>
       </c>
       <c r="D75" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E75" s="5" t="inlineStr">
         <is>
-          <t>Hors fiche</t>
+          <t>Vert</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="5" t="inlineStr">
+        <is>
+          <t>F01</t>
+        </is>
+      </c>
+      <c r="B76" s="5" t="inlineStr">
+        <is>
+          <t>C41b</t>
+        </is>
+      </c>
+      <c r="C76" s="5" t="inlineStr">
+        <is>
+          <t>aucun parcours</t>
+        </is>
+      </c>
+      <c r="D76" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E76" s="5" t="inlineStr">
+        <is>
+          <t>Filet technique seul</t>
         </is>
       </c>
     </row>
@@ -3665,7 +4378,7 @@
   <mergeCells count="1">
     <mergeCell ref="A1:E1"/>
   </mergeCells>
-  <conditionalFormatting sqref="E4:E75">
+  <conditionalFormatting sqref="E4:E76">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"Vert"</formula>
     </cfRule>
@@ -3695,7 +4408,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3800,7 +4513,7 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>S05</t>
+          <t>S40</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
@@ -4014,7 +4727,7 @@
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>Recette S01, S05</t>
+          <t>Recette S01 et S10</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
@@ -4024,7 +4737,7 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>S01 et S05, joués en parallèle</t>
+          <t>S01 et S10, joués en parallèle</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
@@ -4046,7 +4759,7 @@
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>Recette S08</t>
+          <t>Recette S50</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
@@ -4056,7 +4769,7 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>S08</t>
+          <t>S50</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
@@ -4078,7 +4791,7 @@
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>Recette S22</t>
+          <t>Recette S26</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
@@ -4088,7 +4801,7 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>S22</t>
+          <t>S31</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
@@ -4105,12 +4818,12 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>L'accueil détenait `users.exporter` sans `users.consulter` : un droit inopérant, qui s'activait dès qu'on lui accordait la simple lecture</t>
+          <t>L'accueil détenait users.exporter sans users.consulter : un droit inopérant, qui s'activait dès qu'on lui accordait la simple lecture</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>Question soulevée par la recette S08, démontrée par l'API</t>
+          <t>Question soulevée par la recette S50, démontrée par l'API</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
@@ -4129,8 +4842,40 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>F01</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>La pagination était de façade : toute la liste remontait, découpée en mémoire</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>Revue de code sur demande d'Omar</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>Une liste de mille comptes traverse l'application pour en afficher vingt</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>Tests techniques `UsersApiTest.c40` et `PaginationTest`</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>Close</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="F4:F15">
+  <conditionalFormatting sqref="F4:F16">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"Close"</formula>
     </cfRule>
